--- a/Core/Inc/ds_lookup_01_05.xlsx
+++ b/Core/Inc/ds_lookup_01_05.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\res\STM32CubeIDE\workspace_1.12.0\bms-blk\Core\Inc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A389C624-EE41-4D49-92BF-082D87E92434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834B7DFB-CE4A-4ABF-AB6E-CFD25EAAD109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41670" yWindow="2100" windowWidth="28800" windowHeight="15435" activeTab="1" xr2:uid="{D4473AF3-D1EF-406D-B595-001F811C9F16}"/>
+    <workbookView xWindow="7350" yWindow="345" windowWidth="28800" windowHeight="19770" xr2:uid="{D4473AF3-D1EF-406D-B595-001F811C9F16}"/>
   </bookViews>
   <sheets>
-    <sheet name="BAT1_BLK01 (2)" sheetId="4" r:id="rId1"/>
-    <sheet name="BAT1_BRD_05" sheetId="3" r:id="rId2"/>
-    <sheet name="BAT1_BLK04" sheetId="1" r:id="rId3"/>
-    <sheet name="BAT1_BLK05" sheetId="2" r:id="rId4"/>
+    <sheet name="BAT2_BRD_07" sheetId="5" r:id="rId1"/>
+    <sheet name="BAT1_BLK01 (2)" sheetId="4" r:id="rId2"/>
+    <sheet name="BAT1_BRD_05" sheetId="3" r:id="rId3"/>
+    <sheet name="BAT1_BLK04" sheetId="1" r:id="rId4"/>
+    <sheet name="BAT1_BLK05" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="167">
   <si>
     <t>0x28</t>
   </si>
@@ -469,16 +470,91 @@
   </si>
   <si>
     <t>onboard_temp</t>
+  </si>
+  <si>
+    <t>0x39</t>
+  </si>
+  <si>
+    <t>0x56</t>
+  </si>
+  <si>
+    <t>0xD4</t>
+  </si>
+  <si>
+    <t>0xB0</t>
+  </si>
+  <si>
+    <t>0x67</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>0x91</t>
+  </si>
+  <si>
+    <t>0x12</t>
+  </si>
+  <si>
+    <t>0x0A</t>
+  </si>
+  <si>
+    <t>0xEB</t>
+  </si>
+  <si>
+    <t>0xD1</t>
+  </si>
+  <si>
+    <t>0x7F</t>
+  </si>
+  <si>
+    <t>0x19</t>
+  </si>
+  <si>
+    <t>0xED</t>
+  </si>
+  <si>
+    <t>0xB1</t>
+  </si>
+  <si>
+    <t>0x5F</t>
+  </si>
+  <si>
+    <t>0xF3</t>
+  </si>
+  <si>
+    <t>0x48</t>
+  </si>
+  <si>
+    <t>0x43</t>
+  </si>
+  <si>
+    <t>0x8F</t>
+  </si>
+  <si>
+    <t>0x1F</t>
+  </si>
+  <si>
+    <t>0xF7</t>
+  </si>
+  <si>
+    <t>0x13</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -819,6 +895,1449 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35699E4F-4303-4953-AE64-D09B1A493B0E}">
+  <dimension ref="A4:T27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
+    <col min="9" max="9" width="3" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
+    <col min="18" max="18" width="7" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>70</v>
+      </c>
+      <c r="S4" t="s">
+        <v>72</v>
+      </c>
+      <c r="T4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N6" t="s">
+        <v>5</v>
+      </c>
+      <c r="O6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>70</v>
+      </c>
+      <c r="R6" t="s">
+        <v>48</v>
+      </c>
+      <c r="S6" t="s">
+        <v>72</v>
+      </c>
+      <c r="T6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" t="s">
+        <v>12</v>
+      </c>
+      <c r="M7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R7" t="s">
+        <v>146</v>
+      </c>
+      <c r="S7" t="s">
+        <v>72</v>
+      </c>
+      <c r="T7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" t="s">
+        <v>70</v>
+      </c>
+      <c r="N8" t="s">
+        <v>148</v>
+      </c>
+      <c r="O8" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>70</v>
+      </c>
+      <c r="R8" t="s">
+        <v>102</v>
+      </c>
+      <c r="S8" t="s">
+        <v>72</v>
+      </c>
+      <c r="T8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9" t="s">
+        <v>121</v>
+      </c>
+      <c r="O9" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>70</v>
+      </c>
+      <c r="R9" t="s">
+        <v>63</v>
+      </c>
+      <c r="S9" t="s">
+        <v>72</v>
+      </c>
+      <c r="T9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10" t="s">
+        <v>137</v>
+      </c>
+      <c r="O10" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>70</v>
+      </c>
+      <c r="R10" t="s">
+        <v>85</v>
+      </c>
+      <c r="S10" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" t="s">
+        <v>3</v>
+      </c>
+      <c r="K11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" t="s">
+        <v>4</v>
+      </c>
+      <c r="M11" t="s">
+        <v>70</v>
+      </c>
+      <c r="N11" t="s">
+        <v>45</v>
+      </c>
+      <c r="O11" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>70</v>
+      </c>
+      <c r="R11" t="s">
+        <v>151</v>
+      </c>
+      <c r="S11" t="s">
+        <v>72</v>
+      </c>
+      <c r="T11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M12" t="s">
+        <v>70</v>
+      </c>
+      <c r="N12" t="s">
+        <v>149</v>
+      </c>
+      <c r="O12" t="s">
+        <v>70</v>
+      </c>
+      <c r="P12" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>70</v>
+      </c>
+      <c r="R12" t="s">
+        <v>152</v>
+      </c>
+      <c r="S12" t="s">
+        <v>72</v>
+      </c>
+      <c r="T12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13" t="s">
+        <v>3</v>
+      </c>
+      <c r="K13" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" t="s">
+        <v>4</v>
+      </c>
+      <c r="M13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" t="s">
+        <v>153</v>
+      </c>
+      <c r="O13" t="s">
+        <v>70</v>
+      </c>
+      <c r="P13" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>70</v>
+      </c>
+      <c r="R13" t="s">
+        <v>26</v>
+      </c>
+      <c r="S13" t="s">
+        <v>72</v>
+      </c>
+      <c r="T13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" t="s">
+        <v>70</v>
+      </c>
+      <c r="N14" t="s">
+        <v>54</v>
+      </c>
+      <c r="O14" t="s">
+        <v>70</v>
+      </c>
+      <c r="P14" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>70</v>
+      </c>
+      <c r="R14" t="s">
+        <v>73</v>
+      </c>
+      <c r="S14" t="s">
+        <v>72</v>
+      </c>
+      <c r="T14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" t="s">
+        <v>70</v>
+      </c>
+      <c r="N15" t="s">
+        <v>116</v>
+      </c>
+      <c r="O15" t="s">
+        <v>70</v>
+      </c>
+      <c r="P15" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>70</v>
+      </c>
+      <c r="R15" t="s">
+        <v>156</v>
+      </c>
+      <c r="S15" t="s">
+        <v>72</v>
+      </c>
+      <c r="T15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L16" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N16" t="s">
+        <v>149</v>
+      </c>
+      <c r="O16" t="s">
+        <v>70</v>
+      </c>
+      <c r="P16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>70</v>
+      </c>
+      <c r="R16" t="s">
+        <v>28</v>
+      </c>
+      <c r="S16" t="s">
+        <v>72</v>
+      </c>
+      <c r="T16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J17" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" t="s">
+        <v>70</v>
+      </c>
+      <c r="N17" t="s">
+        <v>49</v>
+      </c>
+      <c r="O17" t="s">
+        <v>70</v>
+      </c>
+      <c r="P17" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>70</v>
+      </c>
+      <c r="R17" t="s">
+        <v>157</v>
+      </c>
+      <c r="S17" t="s">
+        <v>72</v>
+      </c>
+      <c r="T17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" t="s">
+        <v>70</v>
+      </c>
+      <c r="J18" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" t="s">
+        <v>49</v>
+      </c>
+      <c r="O18" t="s">
+        <v>70</v>
+      </c>
+      <c r="P18" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>70</v>
+      </c>
+      <c r="R18" t="s">
+        <v>131</v>
+      </c>
+      <c r="S18" t="s">
+        <v>72</v>
+      </c>
+      <c r="T18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" t="s">
+        <v>70</v>
+      </c>
+      <c r="J19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L19" t="s">
+        <v>4</v>
+      </c>
+      <c r="M19" t="s">
+        <v>70</v>
+      </c>
+      <c r="N19" t="s">
+        <v>5</v>
+      </c>
+      <c r="O19" t="s">
+        <v>70</v>
+      </c>
+      <c r="P19" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>70</v>
+      </c>
+      <c r="R19" t="s">
+        <v>159</v>
+      </c>
+      <c r="S19" t="s">
+        <v>72</v>
+      </c>
+      <c r="T19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" t="s">
+        <v>70</v>
+      </c>
+      <c r="N20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O20" t="s">
+        <v>70</v>
+      </c>
+      <c r="P20" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>70</v>
+      </c>
+      <c r="R20" t="s">
+        <v>160</v>
+      </c>
+      <c r="S20" t="s">
+        <v>72</v>
+      </c>
+      <c r="T20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" t="s">
+        <v>70</v>
+      </c>
+      <c r="J21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" t="s">
+        <v>70</v>
+      </c>
+      <c r="L21" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N21" t="s">
+        <v>90</v>
+      </c>
+      <c r="O21" t="s">
+        <v>70</v>
+      </c>
+      <c r="P21" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>70</v>
+      </c>
+      <c r="R21" t="s">
+        <v>26</v>
+      </c>
+      <c r="S21" t="s">
+        <v>72</v>
+      </c>
+      <c r="T21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>17</v>
+      </c>
+      <c r="B22">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" t="s">
+        <v>70</v>
+      </c>
+      <c r="L22" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" t="s">
+        <v>70</v>
+      </c>
+      <c r="N22" t="s">
+        <v>161</v>
+      </c>
+      <c r="O22" t="s">
+        <v>70</v>
+      </c>
+      <c r="P22" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>70</v>
+      </c>
+      <c r="R22" t="s">
+        <v>17</v>
+      </c>
+      <c r="S22" t="s">
+        <v>72</v>
+      </c>
+      <c r="T22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>70</v>
+      </c>
+      <c r="J23" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" t="s">
+        <v>70</v>
+      </c>
+      <c r="L23" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" t="s">
+        <v>70</v>
+      </c>
+      <c r="N23" t="s">
+        <v>162</v>
+      </c>
+      <c r="O23" t="s">
+        <v>70</v>
+      </c>
+      <c r="P23" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>70</v>
+      </c>
+      <c r="R23" t="s">
+        <v>163</v>
+      </c>
+      <c r="S23" t="s">
+        <v>72</v>
+      </c>
+      <c r="T23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>19</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" t="s">
+        <v>70</v>
+      </c>
+      <c r="J24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" t="s">
+        <v>70</v>
+      </c>
+      <c r="L24" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" t="s">
+        <v>70</v>
+      </c>
+      <c r="N24" t="s">
+        <v>107</v>
+      </c>
+      <c r="O24" t="s">
+        <v>70</v>
+      </c>
+      <c r="P24" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>70</v>
+      </c>
+      <c r="R24" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" t="s">
+        <v>72</v>
+      </c>
+      <c r="T24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>20</v>
+      </c>
+      <c r="B25">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" t="s">
+        <v>70</v>
+      </c>
+      <c r="J25" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" t="s">
+        <v>70</v>
+      </c>
+      <c r="L25" t="s">
+        <v>15</v>
+      </c>
+      <c r="M25" t="s">
+        <v>70</v>
+      </c>
+      <c r="N25" t="s">
+        <v>164</v>
+      </c>
+      <c r="O25" t="s">
+        <v>70</v>
+      </c>
+      <c r="P25" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>70</v>
+      </c>
+      <c r="R25" t="s">
+        <v>121</v>
+      </c>
+      <c r="S25" t="s">
+        <v>72</v>
+      </c>
+      <c r="T25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>21</v>
+      </c>
+      <c r="B26">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>70</v>
+      </c>
+      <c r="J26" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" t="s">
+        <v>70</v>
+      </c>
+      <c r="L26" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" t="s">
+        <v>70</v>
+      </c>
+      <c r="N26" t="s">
+        <v>129</v>
+      </c>
+      <c r="O26" t="s">
+        <v>70</v>
+      </c>
+      <c r="P26" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>70</v>
+      </c>
+      <c r="R26" t="s">
+        <v>11</v>
+      </c>
+      <c r="S26" t="s">
+        <v>72</v>
+      </c>
+      <c r="T26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>22</v>
+      </c>
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J27" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" t="s">
+        <v>70</v>
+      </c>
+      <c r="L27" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" t="s">
+        <v>70</v>
+      </c>
+      <c r="N27" t="s">
+        <v>144</v>
+      </c>
+      <c r="O27" t="s">
+        <v>70</v>
+      </c>
+      <c r="P27" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>70</v>
+      </c>
+      <c r="R27" t="s">
+        <v>145</v>
+      </c>
+      <c r="S27" t="s">
+        <v>72</v>
+      </c>
+      <c r="T27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56ACEB68-459E-4B8A-91B6-10D646747FBA}">
   <dimension ref="A4:V27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2260,7 +3779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5CFFDA2-9D8B-4069-AA63-0D049CFF3673}">
   <dimension ref="A4:V4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2353,7 +3872,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8F420D1-D23F-4201-85FC-61080ADED44B}">
   <dimension ref="A4:T26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3741,7 +5260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7B0B922-F444-49EF-A1D0-D03B87F5C0C4}">
   <dimension ref="A4:V26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Core/Inc/ds_lookup_01_05.xlsx
+++ b/Core/Inc/ds_lookup_01_05.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\res\STM32CubeIDE\workspace_1.12.0\bms-blk\Core\Inc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7351C5D-7B72-4D38-810E-4A17ACDFCEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41670" yWindow="2100" windowWidth="28800" windowHeight="15438"/>
+    <workbookView xWindow="43455" yWindow="1080" windowWidth="30450" windowHeight="19770" tabRatio="680" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="BAT1_BLK07" sheetId="9" r:id="rId1"/>
-    <sheet name="BAT1_BLK06" sheetId="8" r:id="rId2"/>
-    <sheet name="BAT1_BLK02" sheetId="7" r:id="rId3"/>
-    <sheet name="BAT1_BLK03" sheetId="6" r:id="rId4"/>
-    <sheet name="BAT1_BLK01" sheetId="4" r:id="rId5"/>
-    <sheet name="BAT1_BLK04" sheetId="1" r:id="rId6"/>
-    <sheet name="BAT1_BLK05" sheetId="2" r:id="rId7"/>
-    <sheet name="BAT1_BRD_04" sheetId="5" r:id="rId8"/>
-    <sheet name="BAT1_BRD_05" sheetId="3" r:id="rId9"/>
+    <sheet name="BAT1_BLK01" sheetId="4" r:id="rId1"/>
+    <sheet name="BAT1_BLK02" sheetId="7" r:id="rId2"/>
+    <sheet name="BAT1_BLK03" sheetId="6" r:id="rId3"/>
+    <sheet name="BAT1_BLK04" sheetId="1" r:id="rId4"/>
+    <sheet name="BAT1_BLK05" sheetId="2" r:id="rId5"/>
+    <sheet name="BAT1_BLK06" sheetId="8" r:id="rId6"/>
+    <sheet name="BAT1_BLK07" sheetId="9" r:id="rId7"/>
+    <sheet name="BAT2_BLK07" sheetId="10" r:id="rId8"/>
+    <sheet name="BAT1_BRD_04" sheetId="5" r:id="rId9"/>
+    <sheet name="BAT1_BRD_05" sheetId="3" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3071" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3467" uniqueCount="229">
   <si>
     <t>0x28</t>
   </si>
@@ -707,12 +709,33 @@
   </si>
   <si>
     <t>0x85</t>
+  </si>
+  <si>
+    <t>0x0A</t>
+  </si>
+  <si>
+    <t>0xEB</t>
+  </si>
+  <si>
+    <t>0xD1</t>
+  </si>
+  <si>
+    <t>0xED</t>
+  </si>
+  <si>
+    <t>0x5F</t>
+  </si>
+  <si>
+    <t>0xF3</t>
+  </si>
+  <si>
+    <t>0x1F</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1071,32 +1094,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:V25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A4:V27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.68359375" customWidth="1"/>
-    <col min="3" max="3" width="2.83984375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="3.26171875" customWidth="1"/>
-    <col min="6" max="6" width="7.15625" customWidth="1"/>
-    <col min="7" max="7" width="2.83984375" customWidth="1"/>
-    <col min="8" max="8" width="6.26171875" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
     <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="2.68359375" customWidth="1"/>
-    <col min="12" max="12" width="5.578125" customWidth="1"/>
-    <col min="13" max="13" width="2.15625" customWidth="1"/>
-    <col min="14" max="14" width="6.68359375" customWidth="1"/>
-    <col min="15" max="15" width="2.83984375" customWidth="1"/>
-    <col min="16" max="16" width="6.15625" customWidth="1"/>
-    <col min="17" max="17" width="2.41796875" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="19" width="3.15625" customWidth="1"/>
-    <col min="20" max="20" width="2.41796875" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -1134,31 +1157,31 @@
         <v>70</v>
       </c>
       <c r="N4" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="O4" t="s">
         <v>70</v>
       </c>
       <c r="P4" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" t="s">
+        <v>127</v>
+      </c>
+      <c r="S4" t="s">
+        <v>72</v>
+      </c>
+      <c r="T4" t="s">
+        <v>70</v>
+      </c>
+      <c r="V4">
         <v>11</v>
       </c>
-      <c r="Q4" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" t="s">
-        <v>58</v>
-      </c>
-      <c r="S4" t="s">
-        <v>72</v>
-      </c>
-      <c r="T4" t="s">
-        <v>70</v>
-      </c>
-      <c r="V4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1196,19 +1219,19 @@
         <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="O5" t="s">
         <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="s">
         <v>70</v>
       </c>
       <c r="R5" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="S5" t="s">
         <v>72</v>
@@ -1217,10 +1240,10 @@
         <v>70</v>
       </c>
       <c r="V5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1258,19 +1281,19 @@
         <v>70</v>
       </c>
       <c r="N6" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="O6" t="s">
         <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>204</v>
+        <v>129</v>
       </c>
       <c r="Q6" t="s">
         <v>70</v>
       </c>
       <c r="R6" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="S6" t="s">
         <v>72</v>
@@ -1279,10 +1302,10 @@
         <v>70</v>
       </c>
       <c r="V6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1320,19 +1343,19 @@
         <v>70</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O7" t="s">
         <v>70</v>
       </c>
       <c r="P7" t="s">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="Q7" t="s">
         <v>70</v>
       </c>
       <c r="R7" t="s">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="S7" t="s">
         <v>72</v>
@@ -1341,10 +1364,10 @@
         <v>70</v>
       </c>
       <c r="V7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -1376,25 +1399,25 @@
         <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M8" t="s">
         <v>70</v>
       </c>
       <c r="N8" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="O8" t="s">
         <v>70</v>
       </c>
       <c r="P8" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="s">
         <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="S8" t="s">
         <v>72</v>
@@ -1403,10 +1426,10 @@
         <v>70</v>
       </c>
       <c r="V8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1438,25 +1461,25 @@
         <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M9" t="s">
         <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="O9" t="s">
         <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="s">
         <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="S9" t="s">
         <v>72</v>
@@ -1465,10 +1488,10 @@
         <v>70</v>
       </c>
       <c r="V9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -1506,19 +1529,19 @@
         <v>70</v>
       </c>
       <c r="N10" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="O10" t="s">
         <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="Q10" t="s">
         <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>208</v>
+        <v>26</v>
       </c>
       <c r="S10" t="s">
         <v>72</v>
@@ -1527,10 +1550,10 @@
         <v>70</v>
       </c>
       <c r="V10">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -1568,19 +1591,19 @@
         <v>70</v>
       </c>
       <c r="N11" t="s">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="O11" t="s">
         <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="Q11" t="s">
         <v>70</v>
       </c>
       <c r="R11" t="s">
-        <v>209</v>
+        <v>136</v>
       </c>
       <c r="S11" t="s">
         <v>72</v>
@@ -1589,10 +1612,10 @@
         <v>70</v>
       </c>
       <c r="V11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -1630,19 +1653,19 @@
         <v>70</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="O12" t="s">
         <v>70</v>
       </c>
       <c r="P12" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="Q12" t="s">
         <v>70</v>
       </c>
       <c r="R12" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="S12" t="s">
         <v>72</v>
@@ -1651,10 +1674,10 @@
         <v>70</v>
       </c>
       <c r="V12">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -1686,25 +1709,25 @@
         <v>70</v>
       </c>
       <c r="L13" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M13" t="s">
         <v>70</v>
       </c>
       <c r="N13" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="O13" t="s">
         <v>70</v>
       </c>
       <c r="P13" t="s">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="Q13" t="s">
         <v>70</v>
       </c>
       <c r="R13" t="s">
-        <v>212</v>
+        <v>80</v>
       </c>
       <c r="S13" t="s">
         <v>72</v>
@@ -1713,10 +1736,10 @@
         <v>70</v>
       </c>
       <c r="V13">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1754,19 +1777,19 @@
         <v>70</v>
       </c>
       <c r="N14" t="s">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="O14" t="s">
         <v>70</v>
       </c>
       <c r="P14" t="s">
-        <v>182</v>
+        <v>6</v>
       </c>
       <c r="Q14" t="s">
         <v>70</v>
       </c>
       <c r="R14" t="s">
-        <v>213</v>
+        <v>140</v>
       </c>
       <c r="S14" t="s">
         <v>72</v>
@@ -1775,10 +1798,10 @@
         <v>70</v>
       </c>
       <c r="V14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -1816,19 +1839,19 @@
         <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>161</v>
+        <v>51</v>
       </c>
       <c r="O15" t="s">
         <v>70</v>
       </c>
       <c r="P15" t="s">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="Q15" t="s">
         <v>70</v>
       </c>
       <c r="R15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="S15" t="s">
         <v>72</v>
@@ -1837,10 +1860,10 @@
         <v>70</v>
       </c>
       <c r="V15">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -1878,19 +1901,19 @@
         <v>70</v>
       </c>
       <c r="N16" t="s">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="O16" t="s">
         <v>70</v>
       </c>
       <c r="P16" t="s">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="Q16" t="s">
         <v>70</v>
       </c>
       <c r="R16" t="s">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="S16" t="s">
         <v>72</v>
@@ -1899,10 +1922,10 @@
         <v>70</v>
       </c>
       <c r="V16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -1940,19 +1963,19 @@
         <v>70</v>
       </c>
       <c r="N17" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="O17" t="s">
         <v>70</v>
       </c>
       <c r="P17" t="s">
-        <v>217</v>
+        <v>123</v>
       </c>
       <c r="Q17" t="s">
         <v>70</v>
       </c>
       <c r="R17" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="S17" t="s">
         <v>72</v>
@@ -1961,10 +1984,10 @@
         <v>70</v>
       </c>
       <c r="V17">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -1996,25 +2019,25 @@
         <v>70</v>
       </c>
       <c r="L18" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M18" t="s">
         <v>70</v>
       </c>
       <c r="N18" t="s">
-        <v>218</v>
+        <v>121</v>
       </c>
       <c r="O18" t="s">
         <v>70</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="Q18" t="s">
         <v>70</v>
       </c>
       <c r="R18" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="S18" t="s">
         <v>72</v>
@@ -2023,10 +2046,10 @@
         <v>70</v>
       </c>
       <c r="V18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -2064,19 +2087,19 @@
         <v>70</v>
       </c>
       <c r="N19" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="O19" t="s">
         <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="Q19" t="s">
         <v>70</v>
       </c>
       <c r="R19" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="S19" t="s">
         <v>72</v>
@@ -2085,10 +2108,10 @@
         <v>70</v>
       </c>
       <c r="V19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -2120,25 +2143,25 @@
         <v>70</v>
       </c>
       <c r="L20" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M20" t="s">
         <v>70</v>
       </c>
       <c r="N20" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="O20" t="s">
         <v>70</v>
       </c>
       <c r="P20" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="Q20" t="s">
         <v>70</v>
       </c>
       <c r="R20" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="S20" t="s">
         <v>72</v>
@@ -2147,10 +2170,10 @@
         <v>70</v>
       </c>
       <c r="V20">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -2188,19 +2211,19 @@
         <v>70</v>
       </c>
       <c r="N21" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="O21" t="s">
         <v>70</v>
       </c>
       <c r="P21" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="Q21" t="s">
         <v>70</v>
       </c>
       <c r="R21" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="S21" t="s">
         <v>72</v>
@@ -2209,10 +2232,10 @@
         <v>70</v>
       </c>
       <c r="V21">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -2250,19 +2273,19 @@
         <v>70</v>
       </c>
       <c r="N22" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="O22" t="s">
         <v>70</v>
       </c>
       <c r="P22" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="Q22" t="s">
         <v>70</v>
       </c>
       <c r="R22" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="S22" t="s">
         <v>72</v>
@@ -2271,10 +2294,10 @@
         <v>70</v>
       </c>
       <c r="V22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -2312,19 +2335,19 @@
         <v>70</v>
       </c>
       <c r="N23" t="s">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="O23" t="s">
         <v>70</v>
       </c>
       <c r="P23" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Q23" t="s">
         <v>70</v>
       </c>
       <c r="R23" t="s">
-        <v>198</v>
+        <v>111</v>
       </c>
       <c r="S23" t="s">
         <v>72</v>
@@ -2336,7 +2359,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -2374,19 +2397,19 @@
         <v>70</v>
       </c>
       <c r="N24" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="O24" t="s">
         <v>70</v>
       </c>
       <c r="P24" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="Q24" t="s">
         <v>70</v>
       </c>
       <c r="R24" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="S24" t="s">
         <v>72</v>
@@ -2395,10 +2418,10 @@
         <v>70</v>
       </c>
       <c r="V24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -2436,19 +2459,19 @@
         <v>70</v>
       </c>
       <c r="N25" t="s">
-        <v>221</v>
+        <v>106</v>
       </c>
       <c r="O25" t="s">
         <v>70</v>
       </c>
       <c r="P25" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="Q25" t="s">
         <v>70</v>
       </c>
       <c r="R25" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="S25" t="s">
         <v>72</v>
@@ -2457,7 +2480,152 @@
         <v>70</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J27" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" t="s">
+        <v>70</v>
+      </c>
+      <c r="M27" t="s">
+        <v>70</v>
+      </c>
+      <c r="O27" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>70</v>
+      </c>
+      <c r="S27" t="s">
+        <v>72</v>
+      </c>
+      <c r="T27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A4:V6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
+    <col min="9" max="9" width="3" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
+    <col min="18" max="18" width="7" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4" t="s">
+        <v>72</v>
+      </c>
+      <c r="T4" t="s">
+        <v>70</v>
+      </c>
+      <c r="V4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2466,32 +2634,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A4:V25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.68359375" customWidth="1"/>
-    <col min="3" max="3" width="2.83984375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="3.26171875" customWidth="1"/>
-    <col min="6" max="6" width="7.15625" customWidth="1"/>
-    <col min="7" max="7" width="2.83984375" customWidth="1"/>
-    <col min="8" max="8" width="6.26171875" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
     <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="2.68359375" customWidth="1"/>
-    <col min="12" max="12" width="5.578125" customWidth="1"/>
-    <col min="13" max="13" width="2.15625" customWidth="1"/>
-    <col min="14" max="14" width="6.68359375" customWidth="1"/>
-    <col min="15" max="15" width="2.83984375" customWidth="1"/>
-    <col min="16" max="16" width="6.15625" customWidth="1"/>
-    <col min="17" max="17" width="2.41796875" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="19" width="3.15625" customWidth="1"/>
-    <col min="20" max="20" width="2.41796875" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -2523,25 +2691,25 @@
         <v>70</v>
       </c>
       <c r="L4" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M4" t="s">
         <v>70</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
+        <v>172</v>
       </c>
       <c r="O4" t="s">
         <v>70</v>
       </c>
       <c r="P4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q4" t="s">
         <v>70</v>
       </c>
       <c r="R4" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="S4" t="s">
         <v>72</v>
@@ -2550,10 +2718,10 @@
         <v>70</v>
       </c>
       <c r="V4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2585,25 +2753,25 @@
         <v>70</v>
       </c>
       <c r="L5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M5" t="s">
         <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="O5" t="s">
         <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="Q5" t="s">
         <v>70</v>
       </c>
       <c r="R5" t="s">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="S5" t="s">
         <v>72</v>
@@ -2612,10 +2780,10 @@
         <v>70</v>
       </c>
       <c r="V5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -2653,19 +2821,19 @@
         <v>70</v>
       </c>
       <c r="N6" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="O6" t="s">
         <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="Q6" t="s">
         <v>70</v>
       </c>
       <c r="R6" t="s">
-        <v>26</v>
+        <v>176</v>
       </c>
       <c r="S6" t="s">
         <v>72</v>
@@ -2674,10 +2842,10 @@
         <v>70</v>
       </c>
       <c r="V6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -2715,19 +2883,19 @@
         <v>70</v>
       </c>
       <c r="N7" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="O7" t="s">
         <v>70</v>
       </c>
       <c r="P7" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="Q7" t="s">
         <v>70</v>
       </c>
       <c r="R7" t="s">
-        <v>194</v>
+        <v>137</v>
       </c>
       <c r="S7" t="s">
         <v>72</v>
@@ -2736,10 +2904,10 @@
         <v>70</v>
       </c>
       <c r="V7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -2771,25 +2939,25 @@
         <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M8" t="s">
         <v>70</v>
       </c>
       <c r="N8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O8" t="s">
         <v>70</v>
       </c>
       <c r="P8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="Q8" t="s">
         <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s">
         <v>72</v>
@@ -2798,10 +2966,10 @@
         <v>70</v>
       </c>
       <c r="V8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -2839,19 +3007,19 @@
         <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="O9" t="s">
         <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="Q9" t="s">
         <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="S9" t="s">
         <v>72</v>
@@ -2860,10 +3028,10 @@
         <v>70</v>
       </c>
       <c r="V9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -2895,25 +3063,25 @@
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M10" t="s">
         <v>70</v>
       </c>
       <c r="N10" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="O10" t="s">
         <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="s">
         <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="S10" t="s">
         <v>72</v>
@@ -2922,10 +3090,10 @@
         <v>70</v>
       </c>
       <c r="V10">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -2963,19 +3131,19 @@
         <v>70</v>
       </c>
       <c r="N11" t="s">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="O11" t="s">
         <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="Q11" t="s">
         <v>70</v>
       </c>
       <c r="R11" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="S11" t="s">
         <v>72</v>
@@ -2984,10 +3152,10 @@
         <v>70</v>
       </c>
       <c r="V11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -3025,19 +3193,19 @@
         <v>70</v>
       </c>
       <c r="N12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="O12" t="s">
         <v>70</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="Q12" t="s">
         <v>70</v>
       </c>
       <c r="R12" t="s">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="S12" t="s">
         <v>72</v>
@@ -3046,10 +3214,10 @@
         <v>70</v>
       </c>
       <c r="V12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -3081,25 +3249,25 @@
         <v>70</v>
       </c>
       <c r="L13" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M13" t="s">
         <v>70</v>
       </c>
       <c r="N13" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="O13" t="s">
         <v>70</v>
       </c>
       <c r="P13" t="s">
-        <v>188</v>
+        <v>121</v>
       </c>
       <c r="Q13" t="s">
         <v>70</v>
       </c>
       <c r="R13" t="s">
-        <v>196</v>
+        <v>52</v>
       </c>
       <c r="S13" t="s">
         <v>72</v>
@@ -3108,10 +3276,10 @@
         <v>70</v>
       </c>
       <c r="V13">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -3149,19 +3317,19 @@
         <v>70</v>
       </c>
       <c r="N14" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="O14" t="s">
         <v>70</v>
       </c>
       <c r="P14" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="Q14" t="s">
         <v>70</v>
       </c>
       <c r="R14" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="S14" t="s">
         <v>72</v>
@@ -3170,10 +3338,10 @@
         <v>70</v>
       </c>
       <c r="V14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -3205,25 +3373,25 @@
         <v>70</v>
       </c>
       <c r="L15" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M15" t="s">
         <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>198</v>
+        <v>5</v>
       </c>
       <c r="O15" t="s">
         <v>70</v>
       </c>
       <c r="P15" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="Q15" t="s">
         <v>70</v>
       </c>
       <c r="R15" t="s">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="S15" t="s">
         <v>72</v>
@@ -3232,10 +3400,10 @@
         <v>70</v>
       </c>
       <c r="V15">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -3273,19 +3441,19 @@
         <v>70</v>
       </c>
       <c r="N16" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="O16" t="s">
         <v>70</v>
       </c>
       <c r="P16" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="Q16" t="s">
         <v>70</v>
       </c>
       <c r="R16" t="s">
-        <v>193</v>
+        <v>41</v>
       </c>
       <c r="S16" t="s">
         <v>72</v>
@@ -3294,10 +3462,10 @@
         <v>70</v>
       </c>
       <c r="V16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -3329,25 +3497,25 @@
         <v>70</v>
       </c>
       <c r="L17" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M17" t="s">
         <v>70</v>
       </c>
       <c r="N17" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="O17" t="s">
         <v>70</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="Q17" t="s">
         <v>70</v>
       </c>
       <c r="R17" t="s">
-        <v>196</v>
+        <v>76</v>
       </c>
       <c r="S17" t="s">
         <v>72</v>
@@ -3356,10 +3524,10 @@
         <v>70</v>
       </c>
       <c r="V17">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -3397,19 +3565,19 @@
         <v>70</v>
       </c>
       <c r="N18" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="O18" t="s">
         <v>70</v>
       </c>
       <c r="P18" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="Q18" t="s">
         <v>70</v>
       </c>
       <c r="R18" t="s">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="S18" t="s">
         <v>72</v>
@@ -3418,10 +3586,10 @@
         <v>70</v>
       </c>
       <c r="V18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -3453,25 +3621,25 @@
         <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M19" t="s">
         <v>70</v>
       </c>
       <c r="N19" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="O19" t="s">
         <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="Q19" t="s">
         <v>70</v>
       </c>
       <c r="R19" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="S19" t="s">
         <v>72</v>
@@ -3480,10 +3648,10 @@
         <v>70</v>
       </c>
       <c r="V19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -3515,25 +3683,25 @@
         <v>70</v>
       </c>
       <c r="L20" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M20" t="s">
         <v>70</v>
       </c>
       <c r="N20" t="s">
-        <v>177</v>
+        <v>45</v>
       </c>
       <c r="O20" t="s">
         <v>70</v>
       </c>
       <c r="P20" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="Q20" t="s">
         <v>70</v>
       </c>
       <c r="R20" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="S20" t="s">
         <v>72</v>
@@ -3542,10 +3710,10 @@
         <v>70</v>
       </c>
       <c r="V20">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -3583,19 +3751,19 @@
         <v>70</v>
       </c>
       <c r="N21" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="O21" t="s">
         <v>70</v>
       </c>
       <c r="P21" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="Q21" t="s">
         <v>70</v>
       </c>
       <c r="R21" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="S21" t="s">
         <v>72</v>
@@ -3604,10 +3772,10 @@
         <v>70</v>
       </c>
       <c r="V21">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -3645,19 +3813,19 @@
         <v>70</v>
       </c>
       <c r="N22" t="s">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="O22" t="s">
         <v>70</v>
       </c>
       <c r="P22" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="Q22" t="s">
         <v>70</v>
       </c>
       <c r="R22" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
       <c r="S22" t="s">
         <v>72</v>
@@ -3666,10 +3834,10 @@
         <v>70</v>
       </c>
       <c r="V22">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -3707,19 +3875,19 @@
         <v>70</v>
       </c>
       <c r="N23" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="O23" t="s">
         <v>70</v>
       </c>
       <c r="P23" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="Q23" t="s">
         <v>70</v>
       </c>
       <c r="R23" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="S23" t="s">
         <v>72</v>
@@ -3728,10 +3896,10 @@
         <v>70</v>
       </c>
       <c r="V23">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -3763,25 +3931,25 @@
         <v>70</v>
       </c>
       <c r="L24" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M24" t="s">
         <v>70</v>
       </c>
       <c r="N24" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="O24" t="s">
         <v>70</v>
       </c>
       <c r="P24" t="s">
-        <v>53</v>
+        <v>181</v>
       </c>
       <c r="Q24" t="s">
         <v>70</v>
       </c>
       <c r="R24" t="s">
-        <v>198</v>
+        <v>129</v>
       </c>
       <c r="S24" t="s">
         <v>72</v>
@@ -3790,10 +3958,10 @@
         <v>70</v>
       </c>
       <c r="V24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -3831,19 +3999,19 @@
         <v>70</v>
       </c>
       <c r="N25" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="O25" t="s">
         <v>70</v>
       </c>
       <c r="P25" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="Q25" t="s">
         <v>70</v>
       </c>
       <c r="R25" t="s">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="S25" t="s">
         <v>72</v>
@@ -3852,7 +4020,7 @@
         <v>70</v>
       </c>
       <c r="V25">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3861,32 +4029,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A4:V25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.68359375" customWidth="1"/>
-    <col min="3" max="3" width="2.83984375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="3.26171875" customWidth="1"/>
-    <col min="6" max="6" width="7.15625" customWidth="1"/>
-    <col min="7" max="7" width="2.83984375" customWidth="1"/>
-    <col min="8" max="8" width="6.26171875" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
     <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="2.68359375" customWidth="1"/>
-    <col min="12" max="12" width="5.578125" customWidth="1"/>
-    <col min="13" max="13" width="2.15625" customWidth="1"/>
-    <col min="14" max="14" width="6.68359375" customWidth="1"/>
-    <col min="15" max="15" width="2.83984375" customWidth="1"/>
-    <col min="16" max="16" width="6.15625" customWidth="1"/>
-    <col min="17" max="17" width="2.41796875" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="19" width="3.15625" customWidth="1"/>
-    <col min="20" max="20" width="2.41796875" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -3918,25 +4086,25 @@
         <v>70</v>
       </c>
       <c r="L4" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M4" t="s">
         <v>70</v>
       </c>
       <c r="N4" t="s">
-        <v>172</v>
+        <v>4</v>
       </c>
       <c r="O4" t="s">
         <v>70</v>
       </c>
       <c r="P4" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="Q4" t="s">
         <v>70</v>
       </c>
       <c r="R4" t="s">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="S4" t="s">
         <v>72</v>
@@ -3945,10 +4113,10 @@
         <v>70</v>
       </c>
       <c r="V4">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3980,161 +4148,161 @@
         <v>70</v>
       </c>
       <c r="L5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" t="s">
+        <v>70</v>
+      </c>
+      <c r="N5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R5" t="s">
+        <v>54</v>
+      </c>
+      <c r="S5" t="s">
+        <v>72</v>
+      </c>
+      <c r="T5" t="s">
+        <v>70</v>
+      </c>
+      <c r="V5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N6" t="s">
+        <v>110</v>
+      </c>
+      <c r="O6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>70</v>
+      </c>
+      <c r="R6" t="s">
+        <v>148</v>
+      </c>
+      <c r="S6" t="s">
+        <v>72</v>
+      </c>
+      <c r="T6" t="s">
+        <v>70</v>
+      </c>
+      <c r="V6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" t="s">
+        <v>149</v>
+      </c>
+      <c r="O7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R7" t="s">
+        <v>94</v>
+      </c>
+      <c r="S7" t="s">
+        <v>72</v>
+      </c>
+      <c r="T7" t="s">
+        <v>70</v>
+      </c>
+      <c r="V7">
         <v>8</v>
       </c>
-      <c r="M5" t="s">
-        <v>70</v>
-      </c>
-      <c r="N5" t="s">
-        <v>173</v>
-      </c>
-      <c r="O5" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>70</v>
-      </c>
-      <c r="R5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S5" t="s">
-        <v>72</v>
-      </c>
-      <c r="T5" t="s">
-        <v>70</v>
-      </c>
-      <c r="V5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M6" t="s">
-        <v>70</v>
-      </c>
-      <c r="N6" t="s">
-        <v>82</v>
-      </c>
-      <c r="O6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>70</v>
-      </c>
-      <c r="R6" t="s">
-        <v>176</v>
-      </c>
-      <c r="S6" t="s">
-        <v>72</v>
-      </c>
-      <c r="T6" t="s">
-        <v>70</v>
-      </c>
-      <c r="V6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" t="s">
-        <v>4</v>
-      </c>
-      <c r="M7" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" t="s">
-        <v>177</v>
-      </c>
-      <c r="O7" t="s">
-        <v>70</v>
-      </c>
-      <c r="P7" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>70</v>
-      </c>
-      <c r="R7" t="s">
-        <v>137</v>
-      </c>
-      <c r="S7" t="s">
-        <v>72</v>
-      </c>
-      <c r="T7" t="s">
-        <v>70</v>
-      </c>
-      <c r="V7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -4166,25 +4334,25 @@
         <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M8" t="s">
         <v>70</v>
       </c>
       <c r="N8" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="O8" t="s">
         <v>70</v>
       </c>
       <c r="P8" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="Q8" t="s">
         <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="S8" t="s">
         <v>72</v>
@@ -4193,10 +4361,10 @@
         <v>70</v>
       </c>
       <c r="V8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -4234,19 +4402,19 @@
         <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="O9" t="s">
         <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="Q9" t="s">
         <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="S9" t="s">
         <v>72</v>
@@ -4255,10 +4423,10 @@
         <v>70</v>
       </c>
       <c r="V9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -4290,25 +4458,25 @@
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M10" t="s">
         <v>70</v>
       </c>
       <c r="N10" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="O10" t="s">
         <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="Q10" t="s">
         <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="S10" t="s">
         <v>72</v>
@@ -4317,10 +4485,10 @@
         <v>70</v>
       </c>
       <c r="V10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -4358,19 +4526,19 @@
         <v>70</v>
       </c>
       <c r="N11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s">
         <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="Q11" t="s">
         <v>70</v>
       </c>
       <c r="R11" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="S11" t="s">
         <v>72</v>
@@ -4379,10 +4547,10 @@
         <v>70</v>
       </c>
       <c r="V11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -4420,19 +4588,19 @@
         <v>70</v>
       </c>
       <c r="N12" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="O12" t="s">
         <v>70</v>
       </c>
       <c r="P12" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="Q12" t="s">
         <v>70</v>
       </c>
       <c r="R12" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="S12" t="s">
         <v>72</v>
@@ -4441,10 +4609,10 @@
         <v>70</v>
       </c>
       <c r="V12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -4482,19 +4650,19 @@
         <v>70</v>
       </c>
       <c r="N13" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="O13" t="s">
         <v>70</v>
       </c>
       <c r="P13" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="Q13" t="s">
         <v>70</v>
       </c>
       <c r="R13" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="S13" t="s">
         <v>72</v>
@@ -4503,10 +4671,10 @@
         <v>70</v>
       </c>
       <c r="V13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -4544,19 +4712,19 @@
         <v>70</v>
       </c>
       <c r="N14" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="O14" t="s">
         <v>70</v>
       </c>
       <c r="P14" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="Q14" t="s">
         <v>70</v>
       </c>
       <c r="R14" t="s">
-        <v>158</v>
+        <v>17</v>
       </c>
       <c r="S14" t="s">
         <v>72</v>
@@ -4565,10 +4733,10 @@
         <v>70</v>
       </c>
       <c r="V14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -4600,25 +4768,25 @@
         <v>70</v>
       </c>
       <c r="L15" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M15" t="s">
         <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>5</v>
+        <v>169</v>
       </c>
       <c r="O15" t="s">
         <v>70</v>
       </c>
       <c r="P15" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="Q15" t="s">
         <v>70</v>
       </c>
       <c r="R15" t="s">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="S15" t="s">
         <v>72</v>
@@ -4627,10 +4795,10 @@
         <v>70</v>
       </c>
       <c r="V15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -4668,19 +4836,19 @@
         <v>70</v>
       </c>
       <c r="N16" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="O16" t="s">
         <v>70</v>
       </c>
       <c r="P16" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="Q16" t="s">
         <v>70</v>
       </c>
       <c r="R16" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="S16" t="s">
         <v>72</v>
@@ -4689,10 +4857,10 @@
         <v>70</v>
       </c>
       <c r="V16">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -4730,19 +4898,19 @@
         <v>70</v>
       </c>
       <c r="N17" t="s">
-        <v>186</v>
+        <v>129</v>
       </c>
       <c r="O17" t="s">
         <v>70</v>
       </c>
       <c r="P17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q17" t="s">
         <v>70</v>
       </c>
       <c r="R17" t="s">
-        <v>76</v>
+        <v>162</v>
       </c>
       <c r="S17" t="s">
         <v>72</v>
@@ -4751,10 +4919,10 @@
         <v>70</v>
       </c>
       <c r="V17">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -4792,19 +4960,19 @@
         <v>70</v>
       </c>
       <c r="N18" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="O18" t="s">
         <v>70</v>
       </c>
       <c r="P18" t="s">
-        <v>91</v>
+        <v>167</v>
       </c>
       <c r="Q18" t="s">
         <v>70</v>
       </c>
       <c r="R18" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="S18" t="s">
         <v>72</v>
@@ -4813,10 +4981,10 @@
         <v>70</v>
       </c>
       <c r="V18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -4848,25 +5016,25 @@
         <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="M19" t="s">
         <v>70</v>
       </c>
       <c r="N19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O19" t="s">
         <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>183</v>
+        <v>48</v>
       </c>
       <c r="Q19" t="s">
         <v>70</v>
       </c>
       <c r="R19" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="S19" t="s">
         <v>72</v>
@@ -4875,10 +5043,10 @@
         <v>70</v>
       </c>
       <c r="V19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -4916,19 +5084,19 @@
         <v>70</v>
       </c>
       <c r="N20" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="O20" t="s">
         <v>70</v>
       </c>
       <c r="P20" t="s">
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="Q20" t="s">
         <v>70</v>
       </c>
       <c r="R20" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="S20" t="s">
         <v>72</v>
@@ -4937,10 +5105,10 @@
         <v>70</v>
       </c>
       <c r="V20">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -4978,19 +5146,19 @@
         <v>70</v>
       </c>
       <c r="N21" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="O21" t="s">
         <v>70</v>
       </c>
       <c r="P21" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="Q21" t="s">
         <v>70</v>
       </c>
       <c r="R21" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="S21" t="s">
         <v>72</v>
@@ -4999,10 +5167,10 @@
         <v>70</v>
       </c>
       <c r="V21">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -5040,19 +5208,19 @@
         <v>70</v>
       </c>
       <c r="N22" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="O22" t="s">
         <v>70</v>
       </c>
       <c r="P22" t="s">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="Q22" t="s">
         <v>70</v>
       </c>
       <c r="R22" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="S22" t="s">
         <v>72</v>
@@ -5061,10 +5229,10 @@
         <v>70</v>
       </c>
       <c r="V22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -5102,19 +5270,19 @@
         <v>70</v>
       </c>
       <c r="N23" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="O23" t="s">
         <v>70</v>
       </c>
       <c r="P23" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="Q23" t="s">
         <v>70</v>
       </c>
       <c r="R23" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="S23" t="s">
         <v>72</v>
@@ -5123,10 +5291,10 @@
         <v>70</v>
       </c>
       <c r="V23">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -5158,25 +5326,25 @@
         <v>70</v>
       </c>
       <c r="L24" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M24" t="s">
         <v>70</v>
       </c>
       <c r="N24" t="s">
-        <v>182</v>
+        <v>32</v>
       </c>
       <c r="O24" t="s">
         <v>70</v>
       </c>
       <c r="P24" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="Q24" t="s">
         <v>70</v>
       </c>
       <c r="R24" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="S24" t="s">
         <v>72</v>
@@ -5185,10 +5353,10 @@
         <v>70</v>
       </c>
       <c r="V24">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -5226,19 +5394,19 @@
         <v>70</v>
       </c>
       <c r="N25" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="O25" t="s">
         <v>70</v>
       </c>
       <c r="P25" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="Q25" t="s">
         <v>70</v>
       </c>
       <c r="R25" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="S25" t="s">
         <v>72</v>
@@ -5247,7 +5415,7 @@
         <v>70</v>
       </c>
       <c r="V25">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -5256,32 +5424,32 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:V25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A4:T26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.68359375" customWidth="1"/>
-    <col min="3" max="3" width="2.83984375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="3.26171875" customWidth="1"/>
-    <col min="6" max="6" width="7.15625" customWidth="1"/>
-    <col min="7" max="7" width="2.83984375" customWidth="1"/>
-    <col min="8" max="8" width="6.26171875" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
     <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="2.68359375" customWidth="1"/>
-    <col min="12" max="12" width="5.578125" customWidth="1"/>
-    <col min="13" max="13" width="2.15625" customWidth="1"/>
-    <col min="14" max="14" width="6.68359375" customWidth="1"/>
-    <col min="15" max="15" width="2.83984375" customWidth="1"/>
-    <col min="16" max="16" width="6.15625" customWidth="1"/>
-    <col min="17" max="17" width="2.41796875" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="19" width="3.15625" customWidth="1"/>
-    <col min="20" max="20" width="2.41796875" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -5313,25 +5481,25 @@
         <v>70</v>
       </c>
       <c r="L4" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="M4" t="s">
         <v>70</v>
       </c>
       <c r="N4" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="O4" t="s">
         <v>70</v>
       </c>
       <c r="P4" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="Q4" t="s">
         <v>70</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="S4" t="s">
         <v>72</v>
@@ -5339,11 +5507,8 @@
       <c r="T4" t="s">
         <v>70</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5381,143 +5546,137 @@
         <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O5" t="s">
         <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="Q5" t="s">
         <v>70</v>
       </c>
       <c r="R5" t="s">
+        <v>61</v>
+      </c>
+      <c r="S5" t="s">
+        <v>72</v>
+      </c>
+      <c r="T5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>70</v>
+      </c>
+      <c r="R6" t="s">
+        <v>59</v>
+      </c>
+      <c r="S6" t="s">
+        <v>72</v>
+      </c>
+      <c r="T6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" t="s">
         <v>54</v>
       </c>
-      <c r="S5" t="s">
-        <v>72</v>
-      </c>
-      <c r="T5" t="s">
-        <v>70</v>
-      </c>
-      <c r="V5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M6" t="s">
-        <v>70</v>
-      </c>
-      <c r="N6" t="s">
-        <v>110</v>
-      </c>
-      <c r="O6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>70</v>
-      </c>
-      <c r="R6" t="s">
-        <v>148</v>
-      </c>
-      <c r="S6" t="s">
-        <v>72</v>
-      </c>
-      <c r="T6" t="s">
-        <v>70</v>
-      </c>
-      <c r="V6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" t="s">
-        <v>4</v>
-      </c>
-      <c r="M7" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" t="s">
-        <v>149</v>
-      </c>
       <c r="O7" t="s">
         <v>70</v>
       </c>
       <c r="P7" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="s">
         <v>70</v>
       </c>
       <c r="R7" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="S7" t="s">
         <v>72</v>
@@ -5525,11 +5684,8 @@
       <c r="T7" t="s">
         <v>70</v>
       </c>
-      <c r="V7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -5567,19 +5723,19 @@
         <v>70</v>
       </c>
       <c r="N8" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
         <v>70</v>
       </c>
       <c r="P8" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="Q8" t="s">
         <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="S8" t="s">
         <v>72</v>
@@ -5587,11 +5743,8 @@
       <c r="T8" t="s">
         <v>70</v>
       </c>
-      <c r="V8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -5623,25 +5776,25 @@
         <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M9" t="s">
         <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="O9" t="s">
         <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="s">
         <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="S9" t="s">
         <v>72</v>
@@ -5649,11 +5802,8 @@
       <c r="T9" t="s">
         <v>70</v>
       </c>
-      <c r="V9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -5685,25 +5835,25 @@
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M10" t="s">
         <v>70</v>
       </c>
       <c r="N10" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="O10" t="s">
         <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="Q10" t="s">
         <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="S10" t="s">
         <v>72</v>
@@ -5711,11 +5861,8 @@
       <c r="T10" t="s">
         <v>70</v>
       </c>
-      <c r="V10">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -5753,19 +5900,19 @@
         <v>70</v>
       </c>
       <c r="N11" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="O11" t="s">
         <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="Q11" t="s">
         <v>70</v>
       </c>
       <c r="R11" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="S11" t="s">
         <v>72</v>
@@ -5773,11 +5920,8 @@
       <c r="T11" t="s">
         <v>70</v>
       </c>
-      <c r="V11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -5815,19 +5959,19 @@
         <v>70</v>
       </c>
       <c r="N12" t="s">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="O12" t="s">
         <v>70</v>
       </c>
       <c r="P12" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="Q12" t="s">
         <v>70</v>
       </c>
       <c r="R12" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="S12" t="s">
         <v>72</v>
@@ -5835,11 +5979,8 @@
       <c r="T12" t="s">
         <v>70</v>
       </c>
-      <c r="V12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -5871,25 +6012,25 @@
         <v>70</v>
       </c>
       <c r="L13" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M13" t="s">
         <v>70</v>
       </c>
       <c r="N13" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="O13" t="s">
         <v>70</v>
       </c>
       <c r="P13" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="Q13" t="s">
         <v>70</v>
       </c>
       <c r="R13" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="S13" t="s">
         <v>72</v>
@@ -5897,11 +6038,8 @@
       <c r="T13" t="s">
         <v>70</v>
       </c>
-      <c r="V13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -5933,25 +6071,25 @@
         <v>70</v>
       </c>
       <c r="L14" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M14" t="s">
         <v>70</v>
       </c>
       <c r="N14" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="O14" t="s">
         <v>70</v>
       </c>
       <c r="P14" t="s">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="Q14" t="s">
         <v>70</v>
       </c>
       <c r="R14" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="S14" t="s">
         <v>72</v>
@@ -5959,11 +6097,8 @@
       <c r="T14" t="s">
         <v>70</v>
       </c>
-      <c r="V14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -5995,25 +6130,25 @@
         <v>70</v>
       </c>
       <c r="L15" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M15" t="s">
         <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>169</v>
+        <v>35</v>
       </c>
       <c r="O15" t="s">
         <v>70</v>
       </c>
       <c r="P15" t="s">
-        <v>170</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="s">
         <v>70</v>
       </c>
       <c r="R15" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="S15" t="s">
         <v>72</v>
@@ -6021,11 +6156,8 @@
       <c r="T15" t="s">
         <v>70</v>
       </c>
-      <c r="V15">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -6063,19 +6195,19 @@
         <v>70</v>
       </c>
       <c r="N16" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="O16" t="s">
         <v>70</v>
       </c>
       <c r="P16" t="s">
-        <v>160</v>
+        <v>33</v>
       </c>
       <c r="Q16" t="s">
         <v>70</v>
       </c>
       <c r="R16" t="s">
-        <v>154</v>
+        <v>34</v>
       </c>
       <c r="S16" t="s">
         <v>72</v>
@@ -6083,11 +6215,8 @@
       <c r="T16" t="s">
         <v>70</v>
       </c>
-      <c r="V16">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -6119,25 +6248,25 @@
         <v>70</v>
       </c>
       <c r="L17" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M17" t="s">
         <v>70</v>
       </c>
       <c r="N17" t="s">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="O17" t="s">
         <v>70</v>
       </c>
       <c r="P17" t="s">
-        <v>161</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="s">
         <v>70</v>
       </c>
       <c r="R17" t="s">
-        <v>162</v>
+        <v>31</v>
       </c>
       <c r="S17" t="s">
         <v>72</v>
@@ -6145,11 +6274,8 @@
       <c r="T17" t="s">
         <v>70</v>
       </c>
-      <c r="V17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -6181,25 +6307,25 @@
         <v>70</v>
       </c>
       <c r="L18" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M18" t="s">
         <v>70</v>
       </c>
       <c r="N18" t="s">
-        <v>166</v>
+        <v>27</v>
       </c>
       <c r="O18" t="s">
         <v>70</v>
       </c>
       <c r="P18" t="s">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Q18" t="s">
         <v>70</v>
       </c>
       <c r="R18" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="S18" t="s">
         <v>72</v>
@@ -6207,11 +6333,8 @@
       <c r="T18" t="s">
         <v>70</v>
       </c>
-      <c r="V18">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -6243,25 +6366,25 @@
         <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="M19" t="s">
         <v>70</v>
       </c>
       <c r="N19" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O19" t="s">
         <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="Q19" t="s">
         <v>70</v>
       </c>
       <c r="R19" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
       <c r="S19" t="s">
         <v>72</v>
@@ -6269,11 +6392,8 @@
       <c r="T19" t="s">
         <v>70</v>
       </c>
-      <c r="V19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -6305,25 +6425,25 @@
         <v>70</v>
       </c>
       <c r="L20" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M20" t="s">
         <v>70</v>
       </c>
       <c r="N20" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="O20" t="s">
         <v>70</v>
       </c>
       <c r="P20" t="s">
-        <v>163</v>
+        <v>22</v>
       </c>
       <c r="Q20" t="s">
         <v>70</v>
       </c>
       <c r="R20" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
       <c r="S20" t="s">
         <v>72</v>
@@ -6331,11 +6451,8 @@
       <c r="T20" t="s">
         <v>70</v>
       </c>
-      <c r="V20">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -6367,25 +6484,25 @@
         <v>70</v>
       </c>
       <c r="L21" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M21" t="s">
         <v>70</v>
       </c>
       <c r="N21" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="O21" t="s">
         <v>70</v>
       </c>
       <c r="P21" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="Q21" t="s">
         <v>70</v>
       </c>
       <c r="R21" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="S21" t="s">
         <v>72</v>
@@ -6393,11 +6510,8 @@
       <c r="T21" t="s">
         <v>70</v>
       </c>
-      <c r="V21">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -6435,19 +6549,19 @@
         <v>70</v>
       </c>
       <c r="N22" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="O22" t="s">
         <v>70</v>
       </c>
       <c r="P22" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="Q22" t="s">
         <v>70</v>
       </c>
       <c r="R22" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="S22" t="s">
         <v>72</v>
@@ -6455,11 +6569,8 @@
       <c r="T22" t="s">
         <v>70</v>
       </c>
-      <c r="V22">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -6491,25 +6602,25 @@
         <v>70</v>
       </c>
       <c r="L23" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M23" t="s">
         <v>70</v>
       </c>
       <c r="N23" t="s">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="O23" t="s">
         <v>70</v>
       </c>
       <c r="P23" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="Q23" t="s">
         <v>70</v>
       </c>
       <c r="R23" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="S23" t="s">
         <v>72</v>
@@ -6517,11 +6628,8 @@
       <c r="T23" t="s">
         <v>70</v>
       </c>
-      <c r="V23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -6553,25 +6661,25 @@
         <v>70</v>
       </c>
       <c r="L24" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M24" t="s">
         <v>70</v>
       </c>
       <c r="N24" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="O24" t="s">
         <v>70</v>
       </c>
       <c r="P24" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="s">
         <v>70</v>
       </c>
       <c r="R24" t="s">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="S24" t="s">
         <v>72</v>
@@ -6579,11 +6687,8 @@
       <c r="T24" t="s">
         <v>70</v>
       </c>
-      <c r="V24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -6621,19 +6726,19 @@
         <v>70</v>
       </c>
       <c r="N25" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="O25" t="s">
         <v>70</v>
       </c>
       <c r="P25" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="s">
         <v>70</v>
       </c>
       <c r="R25" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="S25" t="s">
         <v>72</v>
@@ -6641,8 +6746,64 @@
       <c r="T25" t="s">
         <v>70</v>
       </c>
-      <c r="V25">
-        <v>16</v>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>70</v>
+      </c>
+      <c r="J26" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" t="s">
+        <v>70</v>
+      </c>
+      <c r="L26" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" t="s">
+        <v>70</v>
+      </c>
+      <c r="N26" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" t="s">
+        <v>70</v>
+      </c>
+      <c r="P26" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>70</v>
+      </c>
+      <c r="R26" t="s">
+        <v>44</v>
+      </c>
+      <c r="S26" t="s">
+        <v>72</v>
+      </c>
+      <c r="T26" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -6651,32 +6812,37 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:V27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A2:V26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.68359375" customWidth="1"/>
-    <col min="3" max="3" width="2.83984375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="3.26171875" customWidth="1"/>
-    <col min="6" max="6" width="7.15625" customWidth="1"/>
-    <col min="7" max="7" width="2.83984375" customWidth="1"/>
-    <col min="8" max="8" width="6.26171875" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
     <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="2.68359375" customWidth="1"/>
-    <col min="12" max="12" width="5.578125" customWidth="1"/>
-    <col min="13" max="13" width="2.15625" customWidth="1"/>
-    <col min="14" max="14" width="6.68359375" customWidth="1"/>
-    <col min="15" max="15" width="2.83984375" customWidth="1"/>
-    <col min="16" max="16" width="6.15625" customWidth="1"/>
-    <col min="17" max="17" width="2.41796875" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="19" width="3.15625" customWidth="1"/>
-    <col min="20" max="20" width="2.41796875" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D2" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -6708,25 +6874,25 @@
         <v>70</v>
       </c>
       <c r="L4" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="M4" t="s">
         <v>70</v>
       </c>
       <c r="N4" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="O4" t="s">
         <v>70</v>
       </c>
       <c r="P4" t="s">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="s">
         <v>70</v>
       </c>
       <c r="R4" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="S4" t="s">
         <v>72</v>
@@ -6734,11 +6900,8 @@
       <c r="T4" t="s">
         <v>70</v>
       </c>
-      <c r="V4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6770,161 +6933,152 @@
         <v>70</v>
       </c>
       <c r="L5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M5" t="s">
         <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="O5" t="s">
         <v>70</v>
       </c>
       <c r="P5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R5" t="s">
+        <v>100</v>
+      </c>
+      <c r="S5" t="s">
+        <v>72</v>
+      </c>
+      <c r="T5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>70</v>
+      </c>
+      <c r="R6" t="s">
+        <v>82</v>
+      </c>
+      <c r="S6" t="s">
+        <v>72</v>
+      </c>
+      <c r="T6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" t="s">
+        <v>98</v>
+      </c>
+      <c r="O7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R7" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" t="s">
-        <v>70</v>
-      </c>
-      <c r="R5" t="s">
-        <v>128</v>
-      </c>
-      <c r="S5" t="s">
-        <v>72</v>
-      </c>
-      <c r="T5" t="s">
-        <v>70</v>
-      </c>
-      <c r="V5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M6" t="s">
-        <v>70</v>
-      </c>
-      <c r="N6" t="s">
-        <v>34</v>
-      </c>
-      <c r="O6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>70</v>
-      </c>
-      <c r="R6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S6" t="s">
-        <v>72</v>
-      </c>
-      <c r="T6" t="s">
-        <v>70</v>
-      </c>
-      <c r="V6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" t="s">
-        <v>4</v>
-      </c>
-      <c r="M7" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" t="s">
-        <v>70</v>
-      </c>
-      <c r="P7" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>70</v>
-      </c>
-      <c r="R7" t="s">
-        <v>73</v>
-      </c>
       <c r="S7" t="s">
         <v>72</v>
       </c>
       <c r="T7" t="s">
         <v>70</v>
       </c>
-      <c r="V7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -6962,19 +7116,19 @@
         <v>70</v>
       </c>
       <c r="N8" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="O8" t="s">
         <v>70</v>
       </c>
       <c r="P8" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="Q8" t="s">
         <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="S8" t="s">
         <v>72</v>
@@ -6982,11 +7136,8 @@
       <c r="T8" t="s">
         <v>70</v>
       </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -7018,25 +7169,25 @@
         <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M9" t="s">
         <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="O9" t="s">
         <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="Q9" t="s">
         <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="S9" t="s">
         <v>72</v>
@@ -7044,11 +7195,8 @@
       <c r="T9" t="s">
         <v>70</v>
       </c>
-      <c r="V9">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -7080,25 +7228,25 @@
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M10" t="s">
         <v>70</v>
       </c>
       <c r="N10" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="O10" t="s">
         <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="Q10" t="s">
         <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="S10" t="s">
         <v>72</v>
@@ -7106,11 +7254,8 @@
       <c r="T10" t="s">
         <v>70</v>
       </c>
-      <c r="V10">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -7148,19 +7293,19 @@
         <v>70</v>
       </c>
       <c r="N11" t="s">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="O11" t="s">
         <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="Q11" t="s">
         <v>70</v>
       </c>
       <c r="R11" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="S11" t="s">
         <v>72</v>
@@ -7168,11 +7313,8 @@
       <c r="T11" t="s">
         <v>70</v>
       </c>
-      <c r="V11">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -7210,19 +7352,19 @@
         <v>70</v>
       </c>
       <c r="N12" t="s">
-        <v>137</v>
+        <v>8</v>
       </c>
       <c r="O12" t="s">
         <v>70</v>
       </c>
       <c r="P12" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="Q12" t="s">
         <v>70</v>
       </c>
       <c r="R12" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="S12" t="s">
         <v>72</v>
@@ -7230,11 +7372,8 @@
       <c r="T12" t="s">
         <v>70</v>
       </c>
-      <c r="V12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -7272,19 +7411,19 @@
         <v>70</v>
       </c>
       <c r="N13" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="O13" t="s">
         <v>70</v>
       </c>
       <c r="P13" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="Q13" t="s">
         <v>70</v>
       </c>
       <c r="R13" t="s">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="S13" t="s">
         <v>72</v>
@@ -7292,11 +7431,8 @@
       <c r="T13" t="s">
         <v>70</v>
       </c>
-      <c r="V13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -7334,19 +7470,19 @@
         <v>70</v>
       </c>
       <c r="N14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O14" t="s">
         <v>70</v>
       </c>
       <c r="P14" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="Q14" t="s">
         <v>70</v>
       </c>
       <c r="R14" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="S14" t="s">
         <v>72</v>
@@ -7354,11 +7490,8 @@
       <c r="T14" t="s">
         <v>70</v>
       </c>
-      <c r="V14">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -7396,19 +7529,19 @@
         <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="O15" t="s">
         <v>70</v>
       </c>
       <c r="P15" t="s">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="Q15" t="s">
         <v>70</v>
       </c>
       <c r="R15" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="S15" t="s">
         <v>72</v>
@@ -7416,11 +7549,8 @@
       <c r="T15" t="s">
         <v>70</v>
       </c>
-      <c r="V15">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -7458,19 +7588,19 @@
         <v>70</v>
       </c>
       <c r="N16" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="O16" t="s">
         <v>70</v>
       </c>
       <c r="P16" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="Q16" t="s">
         <v>70</v>
       </c>
       <c r="R16" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="S16" t="s">
         <v>72</v>
@@ -7479,10 +7609,10 @@
         <v>70</v>
       </c>
       <c r="V16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -7520,19 +7650,19 @@
         <v>70</v>
       </c>
       <c r="N17" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="O17" t="s">
         <v>70</v>
       </c>
       <c r="P17" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="Q17" t="s">
         <v>70</v>
       </c>
       <c r="R17" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="S17" t="s">
         <v>72</v>
@@ -7541,10 +7671,10 @@
         <v>70</v>
       </c>
       <c r="V17">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -7576,25 +7706,25 @@
         <v>70</v>
       </c>
       <c r="L18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M18" t="s">
         <v>70</v>
       </c>
       <c r="N18" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="O18" t="s">
         <v>70</v>
       </c>
       <c r="P18" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="Q18" t="s">
         <v>70</v>
       </c>
       <c r="R18" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="S18" t="s">
         <v>72</v>
@@ -7602,11 +7732,8 @@
       <c r="T18" t="s">
         <v>70</v>
       </c>
-      <c r="V18">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -7638,7 +7765,7 @@
         <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M19" t="s">
         <v>70</v>
@@ -7650,13 +7777,13 @@
         <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="Q19" t="s">
         <v>70</v>
       </c>
       <c r="R19" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="S19" t="s">
         <v>72</v>
@@ -7664,11 +7791,8 @@
       <c r="T19" t="s">
         <v>70</v>
       </c>
-      <c r="V19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -7699,38 +7823,23 @@
       <c r="K20" t="s">
         <v>70</v>
       </c>
-      <c r="L20" t="s">
-        <v>12</v>
-      </c>
       <c r="M20" t="s">
         <v>70</v>
       </c>
-      <c r="N20" t="s">
-        <v>116</v>
-      </c>
       <c r="O20" t="s">
         <v>70</v>
       </c>
-      <c r="P20" t="s">
-        <v>117</v>
-      </c>
       <c r="Q20" t="s">
         <v>70</v>
       </c>
-      <c r="R20" t="s">
-        <v>118</v>
-      </c>
       <c r="S20" t="s">
         <v>72</v>
       </c>
       <c r="T20" t="s">
         <v>70</v>
       </c>
-      <c r="V20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -7761,38 +7870,23 @@
       <c r="K21" t="s">
         <v>70</v>
       </c>
-      <c r="L21" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" t="s">
         <v>70</v>
       </c>
-      <c r="N21" t="s">
-        <v>110</v>
-      </c>
       <c r="O21" t="s">
         <v>70</v>
       </c>
-      <c r="P21" t="s">
-        <v>114</v>
-      </c>
       <c r="Q21" t="s">
         <v>70</v>
       </c>
-      <c r="R21" t="s">
-        <v>115</v>
-      </c>
       <c r="S21" t="s">
         <v>72</v>
       </c>
       <c r="T21" t="s">
         <v>70</v>
       </c>
-      <c r="V21">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -7824,25 +7918,25 @@
         <v>70</v>
       </c>
       <c r="L22" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M22" t="s">
         <v>70</v>
       </c>
       <c r="N22" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="O22" t="s">
         <v>70</v>
       </c>
       <c r="P22" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="Q22" t="s">
         <v>70</v>
       </c>
       <c r="R22" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="S22" t="s">
         <v>72</v>
@@ -7850,11 +7944,8 @@
       <c r="T22" t="s">
         <v>70</v>
       </c>
-      <c r="V22">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -7892,19 +7983,19 @@
         <v>70</v>
       </c>
       <c r="N23" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="O23" t="s">
         <v>70</v>
       </c>
       <c r="P23" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="Q23" t="s">
         <v>70</v>
       </c>
       <c r="R23" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="S23" t="s">
         <v>72</v>
@@ -7912,11 +8003,8 @@
       <c r="T23" t="s">
         <v>70</v>
       </c>
-      <c r="V23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -7954,19 +8042,19 @@
         <v>70</v>
       </c>
       <c r="N24" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="O24" t="s">
         <v>70</v>
       </c>
       <c r="P24" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="Q24" t="s">
         <v>70</v>
       </c>
       <c r="R24" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="S24" t="s">
         <v>72</v>
@@ -7974,11 +8062,8 @@
       <c r="T24" t="s">
         <v>70</v>
       </c>
-      <c r="V24">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -8016,19 +8101,19 @@
         <v>70</v>
       </c>
       <c r="N25" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="O25" t="s">
         <v>70</v>
       </c>
       <c r="P25" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="Q25" t="s">
         <v>70</v>
       </c>
       <c r="R25" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="S25" t="s">
         <v>72</v>
@@ -8036,54 +8121,51 @@
       <c r="T25" t="s">
         <v>70</v>
       </c>
-      <c r="V25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>22</v>
       </c>
-      <c r="C27" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E27" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s">
-        <v>70</v>
-      </c>
-      <c r="H27" t="s">
-        <v>2</v>
-      </c>
-      <c r="I27" t="s">
-        <v>70</v>
-      </c>
-      <c r="J27" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" t="s">
-        <v>70</v>
-      </c>
-      <c r="M27" t="s">
-        <v>70</v>
-      </c>
-      <c r="O27" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>70</v>
-      </c>
-      <c r="S27" t="s">
-        <v>72</v>
-      </c>
-      <c r="T27" t="s">
+      <c r="C26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>70</v>
+      </c>
+      <c r="J26" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" t="s">
+        <v>70</v>
+      </c>
+      <c r="M26" t="s">
+        <v>70</v>
+      </c>
+      <c r="O26" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>70</v>
+      </c>
+      <c r="S26" t="s">
+        <v>72</v>
+      </c>
+      <c r="T26" t="s">
         <v>70</v>
       </c>
     </row>
@@ -8093,32 +8175,32 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:T26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A4:V25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.68359375" customWidth="1"/>
-    <col min="3" max="3" width="2.83984375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="3.26171875" customWidth="1"/>
-    <col min="6" max="6" width="7.15625" customWidth="1"/>
-    <col min="7" max="7" width="2.83984375" customWidth="1"/>
-    <col min="8" max="8" width="6.26171875" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
     <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="2.68359375" customWidth="1"/>
-    <col min="12" max="12" width="5.578125" customWidth="1"/>
-    <col min="13" max="13" width="2.15625" customWidth="1"/>
-    <col min="14" max="14" width="6.68359375" customWidth="1"/>
-    <col min="15" max="15" width="2.83984375" customWidth="1"/>
-    <col min="16" max="16" width="6.15625" customWidth="1"/>
-    <col min="17" max="17" width="2.41796875" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="19" width="3.15625" customWidth="1"/>
-    <col min="20" max="20" width="2.41796875" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -8150,25 +8232,25 @@
         <v>70</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="M4" t="s">
         <v>70</v>
       </c>
       <c r="N4" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="O4" t="s">
         <v>70</v>
       </c>
       <c r="P4" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="s">
         <v>70</v>
       </c>
       <c r="R4" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="S4" t="s">
         <v>72</v>
@@ -8176,8 +8258,11 @@
       <c r="T4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8215,19 +8300,19 @@
         <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O5" t="s">
         <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="Q5" t="s">
         <v>70</v>
       </c>
       <c r="R5" t="s">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="S5" t="s">
         <v>72</v>
@@ -8235,8 +8320,11 @@
       <c r="T5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -8274,19 +8362,19 @@
         <v>70</v>
       </c>
       <c r="N6" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="O6" t="s">
         <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="Q6" t="s">
         <v>70</v>
       </c>
       <c r="R6" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="S6" t="s">
         <v>72</v>
@@ -8294,8 +8382,11 @@
       <c r="T6" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -8333,87 +8424,93 @@
         <v>70</v>
       </c>
       <c r="N7" t="s">
+        <v>181</v>
+      </c>
+      <c r="O7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R7" t="s">
+        <v>194</v>
+      </c>
+      <c r="S7" t="s">
+        <v>72</v>
+      </c>
+      <c r="T7" t="s">
+        <v>70</v>
+      </c>
+      <c r="V7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" t="s">
+        <v>70</v>
+      </c>
+      <c r="N8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>70</v>
+      </c>
+      <c r="R8" t="s">
         <v>54</v>
       </c>
-      <c r="O7" t="s">
-        <v>70</v>
-      </c>
-      <c r="P7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>70</v>
-      </c>
-      <c r="R7" t="s">
-        <v>56</v>
-      </c>
-      <c r="S7" t="s">
-        <v>72</v>
-      </c>
-      <c r="T7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8" t="s">
-        <v>70</v>
-      </c>
-      <c r="J8" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" t="s">
-        <v>70</v>
-      </c>
-      <c r="N8" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" t="s">
-        <v>70</v>
-      </c>
-      <c r="P8" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>70</v>
-      </c>
-      <c r="R8" t="s">
-        <v>53</v>
-      </c>
       <c r="S8" t="s">
         <v>72</v>
       </c>
       <c r="T8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -8445,25 +8542,25 @@
         <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M9" t="s">
         <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="O9" t="s">
         <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="Q9" t="s">
         <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>50</v>
+        <v>195</v>
       </c>
       <c r="S9" t="s">
         <v>72</v>
@@ -8471,8 +8568,11 @@
       <c r="T9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -8504,25 +8604,25 @@
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M10" t="s">
         <v>70</v>
       </c>
       <c r="N10" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="O10" t="s">
         <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="s">
         <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="S10" t="s">
         <v>72</v>
@@ -8530,8 +8630,11 @@
       <c r="T10" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -8575,13 +8678,13 @@
         <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="Q11" t="s">
         <v>70</v>
       </c>
       <c r="R11" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="S11" t="s">
         <v>72</v>
@@ -8589,8 +8692,11 @@
       <c r="T11" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -8628,19 +8734,19 @@
         <v>70</v>
       </c>
       <c r="N12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O12" t="s">
         <v>70</v>
       </c>
       <c r="P12" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="Q12" t="s">
         <v>70</v>
       </c>
       <c r="R12" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="S12" t="s">
         <v>72</v>
@@ -8648,8 +8754,11 @@
       <c r="T12" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -8687,19 +8796,19 @@
         <v>70</v>
       </c>
       <c r="N13" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="O13" t="s">
         <v>70</v>
       </c>
       <c r="P13" t="s">
-        <v>38</v>
+        <v>188</v>
       </c>
       <c r="Q13" t="s">
         <v>70</v>
       </c>
       <c r="R13" t="s">
-        <v>39</v>
+        <v>196</v>
       </c>
       <c r="S13" t="s">
         <v>72</v>
@@ -8707,8 +8816,11 @@
       <c r="T13" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -8740,25 +8852,25 @@
         <v>70</v>
       </c>
       <c r="L14" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M14" t="s">
         <v>70</v>
       </c>
       <c r="N14" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="O14" t="s">
         <v>70</v>
       </c>
       <c r="P14" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="s">
         <v>70</v>
       </c>
       <c r="R14" t="s">
-        <v>68</v>
+        <v>197</v>
       </c>
       <c r="S14" t="s">
         <v>72</v>
@@ -8766,8 +8878,11 @@
       <c r="T14" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -8799,25 +8914,25 @@
         <v>70</v>
       </c>
       <c r="L15" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M15" t="s">
         <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>35</v>
+        <v>198</v>
       </c>
       <c r="O15" t="s">
         <v>70</v>
       </c>
       <c r="P15" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="Q15" t="s">
         <v>70</v>
       </c>
       <c r="R15" t="s">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="S15" t="s">
         <v>72</v>
@@ -8825,8 +8940,11 @@
       <c r="T15" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -8864,19 +8982,19 @@
         <v>70</v>
       </c>
       <c r="N16" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="O16" t="s">
         <v>70</v>
       </c>
       <c r="P16" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="Q16" t="s">
         <v>70</v>
       </c>
       <c r="R16" t="s">
-        <v>34</v>
+        <v>193</v>
       </c>
       <c r="S16" t="s">
         <v>72</v>
@@ -8884,8 +9002,11 @@
       <c r="T16" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -8923,19 +9044,19 @@
         <v>70</v>
       </c>
       <c r="N17" t="s">
-        <v>30</v>
+        <v>198</v>
       </c>
       <c r="O17" t="s">
         <v>70</v>
       </c>
       <c r="P17" t="s">
-        <v>5</v>
+        <v>113</v>
       </c>
       <c r="Q17" t="s">
         <v>70</v>
       </c>
       <c r="R17" t="s">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="S17" t="s">
         <v>72</v>
@@ -8943,8 +9064,11 @@
       <c r="T17" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V17">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -8976,25 +9100,25 @@
         <v>70</v>
       </c>
       <c r="L18" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M18" t="s">
         <v>70</v>
       </c>
       <c r="N18" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="O18" t="s">
         <v>70</v>
       </c>
       <c r="P18" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="Q18" t="s">
         <v>70</v>
       </c>
       <c r="R18" t="s">
-        <v>29</v>
+        <v>200</v>
       </c>
       <c r="S18" t="s">
         <v>72</v>
@@ -9002,8 +9126,11 @@
       <c r="T18" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -9035,25 +9162,25 @@
         <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M19" t="s">
         <v>70</v>
       </c>
       <c r="N19" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="O19" t="s">
         <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>25</v>
+        <v>166</v>
       </c>
       <c r="Q19" t="s">
         <v>70</v>
       </c>
       <c r="R19" t="s">
-        <v>26</v>
+        <v>201</v>
       </c>
       <c r="S19" t="s">
         <v>72</v>
@@ -9061,8 +9188,11 @@
       <c r="T19" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -9094,25 +9224,25 @@
         <v>70</v>
       </c>
       <c r="L20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M20" t="s">
         <v>70</v>
       </c>
       <c r="N20" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="O20" t="s">
         <v>70</v>
       </c>
       <c r="P20" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="Q20" t="s">
         <v>70</v>
       </c>
       <c r="R20" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="S20" t="s">
         <v>72</v>
@@ -9120,8 +9250,11 @@
       <c r="T20" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -9153,25 +9286,25 @@
         <v>70</v>
       </c>
       <c r="L21" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M21" t="s">
         <v>70</v>
       </c>
       <c r="N21" t="s">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="O21" t="s">
         <v>70</v>
       </c>
       <c r="P21" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="Q21" t="s">
         <v>70</v>
       </c>
       <c r="R21" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="S21" t="s">
         <v>72</v>
@@ -9179,8 +9312,11 @@
       <c r="T21" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V21">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -9218,19 +9354,19 @@
         <v>70</v>
       </c>
       <c r="N22" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="O22" t="s">
         <v>70</v>
       </c>
       <c r="P22" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="Q22" t="s">
         <v>70</v>
       </c>
       <c r="R22" t="s">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="S22" t="s">
         <v>72</v>
@@ -9238,8 +9374,11 @@
       <c r="T22" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V22">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -9271,34 +9410,37 @@
         <v>70</v>
       </c>
       <c r="L23" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M23" t="s">
         <v>70</v>
       </c>
       <c r="N23" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="O23" t="s">
         <v>70</v>
       </c>
       <c r="P23" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>70</v>
+      </c>
+      <c r="R23" t="s">
+        <v>178</v>
+      </c>
+      <c r="S23" t="s">
+        <v>72</v>
+      </c>
+      <c r="T23" t="s">
+        <v>70</v>
+      </c>
+      <c r="V23">
         <v>14</v>
       </c>
-      <c r="Q23" t="s">
-        <v>70</v>
-      </c>
-      <c r="R23" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" t="s">
-        <v>72</v>
-      </c>
-      <c r="T23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -9330,25 +9472,25 @@
         <v>70</v>
       </c>
       <c r="L24" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M24" t="s">
         <v>70</v>
       </c>
       <c r="N24" t="s">
-        <v>9</v>
+        <v>187</v>
       </c>
       <c r="O24" t="s">
         <v>70</v>
       </c>
       <c r="P24" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="Q24" t="s">
         <v>70</v>
       </c>
       <c r="R24" t="s">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="S24" t="s">
         <v>72</v>
@@ -9356,8 +9498,11 @@
       <c r="T24" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="V24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -9395,19 +9540,19 @@
         <v>70</v>
       </c>
       <c r="N25" t="s">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c r="O25" t="s">
         <v>70</v>
       </c>
       <c r="P25" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="Q25" t="s">
         <v>70</v>
       </c>
       <c r="R25" t="s">
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="S25" t="s">
         <v>72</v>
@@ -9415,64 +9560,8 @@
       <c r="T25" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>70</v>
-      </c>
-      <c r="F26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" t="s">
-        <v>70</v>
-      </c>
-      <c r="H26" t="s">
-        <v>2</v>
-      </c>
-      <c r="I26" t="s">
-        <v>70</v>
-      </c>
-      <c r="J26" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" t="s">
-        <v>70</v>
-      </c>
-      <c r="L26" t="s">
-        <v>4</v>
-      </c>
-      <c r="M26" t="s">
-        <v>70</v>
-      </c>
-      <c r="N26" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" t="s">
-        <v>70</v>
-      </c>
-      <c r="P26" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>70</v>
-      </c>
-      <c r="R26" t="s">
-        <v>44</v>
-      </c>
-      <c r="S26" t="s">
-        <v>72</v>
-      </c>
-      <c r="T26" t="s">
-        <v>70</v>
+      <c r="V25">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -9481,37 +9570,32 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:V26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A4:V25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.68359375" customWidth="1"/>
-    <col min="3" max="3" width="2.83984375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="3.26171875" customWidth="1"/>
-    <col min="6" max="6" width="7.15625" customWidth="1"/>
-    <col min="7" max="7" width="2.83984375" customWidth="1"/>
-    <col min="8" max="8" width="6.26171875" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
     <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="2.68359375" customWidth="1"/>
-    <col min="12" max="12" width="5.578125" customWidth="1"/>
-    <col min="13" max="13" width="2.15625" customWidth="1"/>
-    <col min="14" max="14" width="6.68359375" customWidth="1"/>
-    <col min="15" max="15" width="2.83984375" customWidth="1"/>
-    <col min="16" max="16" width="6.15625" customWidth="1"/>
-    <col min="17" max="17" width="2.41796875" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="19" width="3.15625" customWidth="1"/>
-    <col min="20" max="20" width="2.41796875" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="D2" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -9543,13 +9627,13 @@
         <v>70</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="M4" t="s">
         <v>70</v>
       </c>
       <c r="N4" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="O4" t="s">
         <v>70</v>
@@ -9561,7 +9645,7 @@
         <v>70</v>
       </c>
       <c r="R4" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="S4" t="s">
         <v>72</v>
@@ -9569,8 +9653,11 @@
       <c r="T4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -9602,25 +9689,25 @@
         <v>70</v>
       </c>
       <c r="L5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M5" t="s">
         <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="O5" t="s">
         <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="Q5" t="s">
         <v>70</v>
       </c>
       <c r="R5" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="S5" t="s">
         <v>72</v>
@@ -9628,8 +9715,11 @@
       <c r="T5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -9667,19 +9757,19 @@
         <v>70</v>
       </c>
       <c r="N6" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="O6" t="s">
         <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="Q6" t="s">
         <v>70</v>
       </c>
       <c r="R6" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="S6" t="s">
         <v>72</v>
@@ -9687,8 +9777,11 @@
       <c r="T6" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -9726,19 +9819,19 @@
         <v>70</v>
       </c>
       <c r="N7" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="O7" t="s">
         <v>70</v>
       </c>
       <c r="P7" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="Q7" t="s">
         <v>70</v>
       </c>
       <c r="R7" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="S7" t="s">
         <v>72</v>
@@ -9746,8 +9839,11 @@
       <c r="T7" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -9779,25 +9875,25 @@
         <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M8" t="s">
         <v>70</v>
       </c>
       <c r="N8" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="O8" t="s">
         <v>70</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>206</v>
       </c>
       <c r="Q8" t="s">
         <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>97</v>
+        <v>207</v>
       </c>
       <c r="S8" t="s">
         <v>72</v>
@@ -9805,8 +9901,11 @@
       <c r="T8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -9844,19 +9943,19 @@
         <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="O9" t="s">
         <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="Q9" t="s">
         <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="S9" t="s">
         <v>72</v>
@@ -9864,8 +9963,11 @@
       <c r="T9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -9897,25 +9999,25 @@
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M10" t="s">
         <v>70</v>
       </c>
       <c r="N10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O10" t="s">
         <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="Q10" t="s">
         <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="S10" t="s">
         <v>72</v>
@@ -9923,8 +10025,11 @@
       <c r="T10" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -9962,19 +10067,19 @@
         <v>70</v>
       </c>
       <c r="N11" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="O11" t="s">
         <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>93</v>
+        <v>206</v>
       </c>
       <c r="Q11" t="s">
         <v>70</v>
       </c>
       <c r="R11" t="s">
-        <v>10</v>
+        <v>209</v>
       </c>
       <c r="S11" t="s">
         <v>72</v>
@@ -9982,8 +10087,11 @@
       <c r="T11" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -10021,19 +10129,19 @@
         <v>70</v>
       </c>
       <c r="N12" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="O12" t="s">
         <v>70</v>
       </c>
       <c r="P12" t="s">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="Q12" t="s">
         <v>70</v>
       </c>
       <c r="R12" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="S12" t="s">
         <v>72</v>
@@ -10041,8 +10149,11 @@
       <c r="T12" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -10074,25 +10185,25 @@
         <v>70</v>
       </c>
       <c r="L13" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M13" t="s">
         <v>70</v>
       </c>
       <c r="N13" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="O13" t="s">
         <v>70</v>
       </c>
       <c r="P13" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="Q13" t="s">
         <v>70</v>
       </c>
       <c r="R13" t="s">
-        <v>10</v>
+        <v>212</v>
       </c>
       <c r="S13" t="s">
         <v>72</v>
@@ -10100,8 +10211,11 @@
       <c r="T13" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -10139,19 +10253,19 @@
         <v>70</v>
       </c>
       <c r="N14" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="O14" t="s">
         <v>70</v>
       </c>
       <c r="P14" t="s">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="Q14" t="s">
         <v>70</v>
       </c>
       <c r="R14" t="s">
-        <v>88</v>
+        <v>213</v>
       </c>
       <c r="S14" t="s">
         <v>72</v>
@@ -10159,8 +10273,11 @@
       <c r="T14" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -10198,19 +10315,19 @@
         <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="O15" t="s">
         <v>70</v>
       </c>
       <c r="P15" t="s">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="Q15" t="s">
         <v>70</v>
       </c>
       <c r="R15" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="S15" t="s">
         <v>72</v>
@@ -10218,8 +10335,11 @@
       <c r="T15" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -10257,19 +10377,19 @@
         <v>70</v>
       </c>
       <c r="N16" t="s">
-        <v>104</v>
+        <v>215</v>
       </c>
       <c r="O16" t="s">
         <v>70</v>
       </c>
       <c r="P16" t="s">
-        <v>105</v>
+        <v>216</v>
       </c>
       <c r="Q16" t="s">
         <v>70</v>
       </c>
       <c r="R16" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="S16" t="s">
         <v>72</v>
@@ -10278,10 +10398,10 @@
         <v>70</v>
       </c>
       <c r="V16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -10319,19 +10439,19 @@
         <v>70</v>
       </c>
       <c r="N17" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="O17" t="s">
         <v>70</v>
       </c>
       <c r="P17" t="s">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="Q17" t="s">
         <v>70</v>
       </c>
       <c r="R17" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="S17" t="s">
         <v>72</v>
@@ -10340,10 +10460,10 @@
         <v>70</v>
       </c>
       <c r="V17">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -10375,25 +10495,25 @@
         <v>70</v>
       </c>
       <c r="L18" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M18" t="s">
         <v>70</v>
       </c>
       <c r="N18" t="s">
-        <v>84</v>
+        <v>218</v>
       </c>
       <c r="O18" t="s">
         <v>70</v>
       </c>
       <c r="P18" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q18" t="s">
         <v>70</v>
       </c>
       <c r="R18" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="S18" t="s">
         <v>72</v>
@@ -10401,8 +10521,11 @@
       <c r="T18" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -10434,25 +10557,25 @@
         <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M19" t="s">
         <v>70</v>
       </c>
       <c r="N19" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="O19" t="s">
         <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="Q19" t="s">
         <v>70</v>
       </c>
       <c r="R19" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="S19" t="s">
         <v>72</v>
@@ -10460,8 +10583,11 @@
       <c r="T19" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -10492,23 +10618,38 @@
       <c r="K20" t="s">
         <v>70</v>
       </c>
+      <c r="L20" t="s">
+        <v>8</v>
+      </c>
       <c r="M20" t="s">
         <v>70</v>
       </c>
+      <c r="N20" t="s">
+        <v>220</v>
+      </c>
       <c r="O20" t="s">
         <v>70</v>
       </c>
+      <c r="P20" t="s">
+        <v>10</v>
+      </c>
       <c r="Q20" t="s">
         <v>70</v>
       </c>
+      <c r="R20" t="s">
+        <v>124</v>
+      </c>
       <c r="S20" t="s">
         <v>72</v>
       </c>
       <c r="T20" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -10539,23 +10680,38 @@
       <c r="K21" t="s">
         <v>70</v>
       </c>
+      <c r="L21" t="s">
+        <v>4</v>
+      </c>
       <c r="M21" t="s">
         <v>70</v>
       </c>
+      <c r="N21" t="s">
+        <v>137</v>
+      </c>
       <c r="O21" t="s">
         <v>70</v>
       </c>
+      <c r="P21" t="s">
+        <v>139</v>
+      </c>
       <c r="Q21" t="s">
         <v>70</v>
       </c>
+      <c r="R21" t="s">
+        <v>146</v>
+      </c>
       <c r="S21" t="s">
         <v>72</v>
       </c>
       <c r="T21" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -10587,25 +10743,25 @@
         <v>70</v>
       </c>
       <c r="L22" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M22" t="s">
         <v>70</v>
       </c>
       <c r="N22" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="O22" t="s">
         <v>70</v>
       </c>
       <c r="P22" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="Q22" t="s">
         <v>70</v>
       </c>
       <c r="R22" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="S22" t="s">
         <v>72</v>
@@ -10613,8 +10769,11 @@
       <c r="T22" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -10652,19 +10811,19 @@
         <v>70</v>
       </c>
       <c r="N23" t="s">
-        <v>75</v>
+        <v>178</v>
       </c>
       <c r="O23" t="s">
         <v>70</v>
       </c>
       <c r="P23" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="Q23" t="s">
         <v>70</v>
       </c>
       <c r="R23" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="S23" t="s">
         <v>72</v>
@@ -10672,8 +10831,11 @@
       <c r="T23" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -10711,19 +10873,19 @@
         <v>70</v>
       </c>
       <c r="N24" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="O24" t="s">
         <v>70</v>
       </c>
       <c r="P24" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="Q24" t="s">
         <v>70</v>
       </c>
       <c r="R24" t="s">
-        <v>4</v>
+        <v>159</v>
       </c>
       <c r="S24" t="s">
         <v>72</v>
@@ -10731,8 +10893,11 @@
       <c r="T24" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -10770,19 +10935,19 @@
         <v>70</v>
       </c>
       <c r="N25" t="s">
-        <v>56</v>
+        <v>221</v>
       </c>
       <c r="O25" t="s">
         <v>70</v>
       </c>
       <c r="P25" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="Q25" t="s">
         <v>70</v>
       </c>
       <c r="R25" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="S25" t="s">
         <v>72</v>
@@ -10790,52 +10955,8 @@
       <c r="T25" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>70</v>
-      </c>
-      <c r="F26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" t="s">
-        <v>70</v>
-      </c>
-      <c r="H26" t="s">
-        <v>2</v>
-      </c>
-      <c r="I26" t="s">
-        <v>70</v>
-      </c>
-      <c r="J26" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" t="s">
-        <v>70</v>
-      </c>
-      <c r="M26" t="s">
-        <v>70</v>
-      </c>
-      <c r="O26" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>70</v>
-      </c>
-      <c r="S26" t="s">
-        <v>72</v>
-      </c>
-      <c r="T26" t="s">
-        <v>70</v>
+      <c r="V25">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10844,37 +10965,1442 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70CB1DAE-36E9-42DC-A7FA-1955404CEAC9}">
+  <dimension ref="A3:V26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.68359375" customWidth="1"/>
-    <col min="3" max="3" width="2.83984375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="3.26171875" customWidth="1"/>
-    <col min="6" max="6" width="7.15625" customWidth="1"/>
-    <col min="7" max="7" width="2.83984375" customWidth="1"/>
-    <col min="8" max="8" width="6.26171875" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
     <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="2.68359375" customWidth="1"/>
-    <col min="12" max="12" width="5.578125" customWidth="1"/>
-    <col min="13" max="13" width="2.15625" customWidth="1"/>
-    <col min="14" max="14" width="6.68359375" customWidth="1"/>
-    <col min="15" max="15" width="2.83984375" customWidth="1"/>
-    <col min="16" max="16" width="6.15625" customWidth="1"/>
-    <col min="17" max="17" width="2.41796875" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="19" width="3.15625" customWidth="1"/>
-    <col min="20" max="20" width="2.41796875" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" t="s">
+        <v>72</v>
+      </c>
+      <c r="T4" t="s">
+        <v>70</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" t="s">
+        <v>70</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R5" t="s">
+        <v>213</v>
+      </c>
+      <c r="S5" t="s">
+        <v>72</v>
+      </c>
+      <c r="T5" t="s">
+        <v>70</v>
+      </c>
+      <c r="V5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N6" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>70</v>
+      </c>
+      <c r="R6" t="s">
+        <v>102</v>
+      </c>
+      <c r="S6" t="s">
+        <v>72</v>
+      </c>
+      <c r="T6" t="s">
+        <v>70</v>
+      </c>
+      <c r="V6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" t="s">
+        <v>121</v>
+      </c>
+      <c r="O7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R7" t="s">
+        <v>63</v>
+      </c>
+      <c r="S7" t="s">
+        <v>72</v>
+      </c>
+      <c r="T7" t="s">
+        <v>70</v>
+      </c>
+      <c r="V7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" t="s">
+        <v>70</v>
+      </c>
+      <c r="N8" t="s">
+        <v>137</v>
+      </c>
+      <c r="O8" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>70</v>
+      </c>
+      <c r="R8" t="s">
+        <v>85</v>
+      </c>
+      <c r="S8" t="s">
+        <v>72</v>
+      </c>
+      <c r="T8" t="s">
+        <v>70</v>
+      </c>
+      <c r="V8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>70</v>
+      </c>
+      <c r="R9" t="s">
+        <v>155</v>
+      </c>
+      <c r="S9" t="s">
+        <v>72</v>
+      </c>
+      <c r="T9" t="s">
+        <v>70</v>
+      </c>
+      <c r="V9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10" t="s">
+        <v>193</v>
+      </c>
+      <c r="O10" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>70</v>
+      </c>
+      <c r="R10" t="s">
+        <v>222</v>
+      </c>
+      <c r="S10" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" t="s">
+        <v>70</v>
+      </c>
+      <c r="V10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" t="s">
+        <v>3</v>
+      </c>
+      <c r="K11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" t="s">
+        <v>4</v>
+      </c>
+      <c r="M11" t="s">
+        <v>70</v>
+      </c>
+      <c r="N11" t="s">
+        <v>223</v>
+      </c>
+      <c r="O11" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>70</v>
+      </c>
+      <c r="R11" t="s">
+        <v>26</v>
+      </c>
+      <c r="S11" t="s">
+        <v>72</v>
+      </c>
+      <c r="T11" t="s">
+        <v>70</v>
+      </c>
+      <c r="V11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" t="s">
+        <v>70</v>
+      </c>
+      <c r="N12" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" t="s">
+        <v>70</v>
+      </c>
+      <c r="P12" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>70</v>
+      </c>
+      <c r="R12" t="s">
+        <v>73</v>
+      </c>
+      <c r="S12" t="s">
+        <v>72</v>
+      </c>
+      <c r="T12" t="s">
+        <v>70</v>
+      </c>
+      <c r="V12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13" t="s">
+        <v>3</v>
+      </c>
+      <c r="K13" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" t="s">
+        <v>116</v>
+      </c>
+      <c r="O13" t="s">
+        <v>70</v>
+      </c>
+      <c r="P13" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>70</v>
+      </c>
+      <c r="R13" t="s">
+        <v>151</v>
+      </c>
+      <c r="S13" t="s">
+        <v>72</v>
+      </c>
+      <c r="T13" t="s">
+        <v>70</v>
+      </c>
+      <c r="V13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" t="s">
+        <v>70</v>
+      </c>
+      <c r="N14" t="s">
+        <v>193</v>
+      </c>
+      <c r="O14" t="s">
+        <v>70</v>
+      </c>
+      <c r="P14" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>70</v>
+      </c>
+      <c r="R14" t="s">
+        <v>28</v>
+      </c>
+      <c r="S14" t="s">
+        <v>72</v>
+      </c>
+      <c r="T14" t="s">
+        <v>70</v>
+      </c>
+      <c r="V14">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" t="s">
+        <v>70</v>
+      </c>
+      <c r="N15" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" t="s">
+        <v>70</v>
+      </c>
+      <c r="P15" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>70</v>
+      </c>
+      <c r="R15" t="s">
+        <v>225</v>
+      </c>
+      <c r="S15" t="s">
+        <v>72</v>
+      </c>
+      <c r="T15" t="s">
+        <v>70</v>
+      </c>
+      <c r="V15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L16" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N16" t="s">
+        <v>49</v>
+      </c>
+      <c r="O16" t="s">
+        <v>70</v>
+      </c>
+      <c r="P16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>70</v>
+      </c>
+      <c r="R16" t="s">
+        <v>131</v>
+      </c>
+      <c r="S16" t="s">
+        <v>72</v>
+      </c>
+      <c r="T16" t="s">
+        <v>70</v>
+      </c>
+      <c r="V16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J17" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" t="s">
+        <v>70</v>
+      </c>
+      <c r="N17" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" t="s">
+        <v>70</v>
+      </c>
+      <c r="P17" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>70</v>
+      </c>
+      <c r="R17" t="s">
+        <v>226</v>
+      </c>
+      <c r="S17" t="s">
+        <v>72</v>
+      </c>
+      <c r="T17" t="s">
+        <v>70</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" t="s">
+        <v>70</v>
+      </c>
+      <c r="J18" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O18" t="s">
+        <v>70</v>
+      </c>
+      <c r="P18" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>70</v>
+      </c>
+      <c r="R18" t="s">
+        <v>227</v>
+      </c>
+      <c r="S18" t="s">
+        <v>72</v>
+      </c>
+      <c r="T18" t="s">
+        <v>70</v>
+      </c>
+      <c r="V18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" t="s">
+        <v>70</v>
+      </c>
+      <c r="J19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L19" t="s">
+        <v>4</v>
+      </c>
+      <c r="M19" t="s">
+        <v>70</v>
+      </c>
+      <c r="N19" t="s">
+        <v>90</v>
+      </c>
+      <c r="O19" t="s">
+        <v>70</v>
+      </c>
+      <c r="P19" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>70</v>
+      </c>
+      <c r="R19" t="s">
+        <v>26</v>
+      </c>
+      <c r="S19" t="s">
+        <v>72</v>
+      </c>
+      <c r="T19" t="s">
+        <v>70</v>
+      </c>
+      <c r="V19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" t="s">
+        <v>70</v>
+      </c>
+      <c r="N20" t="s">
+        <v>161</v>
+      </c>
+      <c r="O20" t="s">
+        <v>70</v>
+      </c>
+      <c r="P20" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>70</v>
+      </c>
+      <c r="R20" t="s">
+        <v>17</v>
+      </c>
+      <c r="S20" t="s">
+        <v>72</v>
+      </c>
+      <c r="T20" t="s">
+        <v>70</v>
+      </c>
+      <c r="V20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" t="s">
+        <v>70</v>
+      </c>
+      <c r="J21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" t="s">
+        <v>70</v>
+      </c>
+      <c r="L21" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N21" t="s">
+        <v>150</v>
+      </c>
+      <c r="O21" t="s">
+        <v>70</v>
+      </c>
+      <c r="P21" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>70</v>
+      </c>
+      <c r="R21" t="s">
+        <v>176</v>
+      </c>
+      <c r="S21" t="s">
+        <v>72</v>
+      </c>
+      <c r="T21" t="s">
+        <v>70</v>
+      </c>
+      <c r="V21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" t="s">
+        <v>70</v>
+      </c>
+      <c r="L22" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" t="s">
+        <v>70</v>
+      </c>
+      <c r="N22" t="s">
+        <v>107</v>
+      </c>
+      <c r="O22" t="s">
+        <v>70</v>
+      </c>
+      <c r="P22" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>70</v>
+      </c>
+      <c r="R22" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" t="s">
+        <v>72</v>
+      </c>
+      <c r="T22" t="s">
+        <v>70</v>
+      </c>
+      <c r="V22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>70</v>
+      </c>
+      <c r="J23" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" t="s">
+        <v>70</v>
+      </c>
+      <c r="L23" t="s">
+        <v>15</v>
+      </c>
+      <c r="M23" t="s">
+        <v>70</v>
+      </c>
+      <c r="N23" t="s">
+        <v>228</v>
+      </c>
+      <c r="O23" t="s">
+        <v>70</v>
+      </c>
+      <c r="P23" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>70</v>
+      </c>
+      <c r="R23" t="s">
+        <v>121</v>
+      </c>
+      <c r="S23" t="s">
+        <v>72</v>
+      </c>
+      <c r="T23" t="s">
+        <v>70</v>
+      </c>
+      <c r="V23">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" t="s">
+        <v>70</v>
+      </c>
+      <c r="J24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" t="s">
+        <v>70</v>
+      </c>
+      <c r="L24" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" t="s">
+        <v>70</v>
+      </c>
+      <c r="N24" t="s">
+        <v>129</v>
+      </c>
+      <c r="O24" t="s">
+        <v>70</v>
+      </c>
+      <c r="P24" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>70</v>
+      </c>
+      <c r="R24" t="s">
+        <v>11</v>
+      </c>
+      <c r="S24" t="s">
+        <v>72</v>
+      </c>
+      <c r="T24" t="s">
+        <v>70</v>
+      </c>
+      <c r="V24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" t="s">
+        <v>70</v>
+      </c>
+      <c r="J25" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" t="s">
+        <v>70</v>
+      </c>
+      <c r="L25" t="s">
+        <v>4</v>
+      </c>
+      <c r="M25" t="s">
+        <v>70</v>
+      </c>
+      <c r="N25" t="s">
+        <v>215</v>
+      </c>
+      <c r="O25" t="s">
+        <v>70</v>
+      </c>
+      <c r="P25" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>70</v>
+      </c>
+      <c r="R25" t="s">
+        <v>220</v>
+      </c>
+      <c r="S25" t="s">
+        <v>72</v>
+      </c>
+      <c r="T25" t="s">
+        <v>70</v>
+      </c>
+      <c r="V25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V26">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:V22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
+    <col min="9" max="9" width="3" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" customWidth="1"/>
+    <col min="17" max="17" width="2.42578125" customWidth="1"/>
+    <col min="18" max="18" width="7" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" customWidth="1"/>
+    <col min="20" max="20" width="2.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -10921,7 +12447,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -10980,7 +12506,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -11039,7 +12565,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -11101,7 +12627,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -11160,7 +12686,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -11207,7 +12733,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -11254,12 +12780,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
@@ -11318,7 +12844,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -11377,7 +12903,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>3</v>
       </c>
@@ -11436,7 +12962,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>4</v>
       </c>
@@ -11495,7 +13021,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>5</v>
       </c>
@@ -11545,7 +13071,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>6</v>
       </c>
@@ -11604,7 +13130,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>7</v>
       </c>
@@ -11667,102 +13193,4 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:V6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="2" max="2" width="3.68359375" customWidth="1"/>
-    <col min="3" max="3" width="2.83984375" customWidth="1"/>
-    <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="3.26171875" customWidth="1"/>
-    <col min="6" max="6" width="7.15625" customWidth="1"/>
-    <col min="7" max="7" width="2.83984375" customWidth="1"/>
-    <col min="8" max="8" width="6.26171875" customWidth="1"/>
-    <col min="9" max="9" width="3" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="2.68359375" customWidth="1"/>
-    <col min="12" max="12" width="5.578125" customWidth="1"/>
-    <col min="13" max="13" width="2.15625" customWidth="1"/>
-    <col min="14" max="14" width="6.68359375" customWidth="1"/>
-    <col min="15" max="15" width="2.83984375" customWidth="1"/>
-    <col min="16" max="16" width="6.15625" customWidth="1"/>
-    <col min="17" max="17" width="2.41796875" customWidth="1"/>
-    <col min="18" max="18" width="7" customWidth="1"/>
-    <col min="19" max="19" width="3.15625" customWidth="1"/>
-    <col min="20" max="20" width="2.41796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M4" t="s">
-        <v>70</v>
-      </c>
-      <c r="N4" t="s">
-        <v>5</v>
-      </c>
-      <c r="O4" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" t="s">
-        <v>72</v>
-      </c>
-      <c r="T4" t="s">
-        <v>70</v>
-      </c>
-      <c r="V4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>